--- a/ftu_students_all.xlsx
+++ b/ftu_students_all.xlsx
@@ -401,19 +401,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>StudentID</v>
+        <v>studentId</v>
       </c>
       <c r="B1" t="str">
-        <v>Name</v>
+        <v>name</v>
       </c>
       <c r="C1" t="str">
-        <v>Major</v>
+        <v>major</v>
       </c>
       <c r="D1" t="str">
-        <v>AcademicYear</v>
+        <v>academicYear</v>
       </c>
       <c r="E1" t="str">
-        <v>YearLevel</v>
+        <v>yearLevel</v>
       </c>
     </row>
     <row r="2">
@@ -424,7 +424,7 @@
         <v>นายชาฝีอี มินยุนุ้ย</v>
       </c>
       <c r="C2" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D2" t="str">
         <v>2565</v>
@@ -441,7 +441,7 @@
         <v>นายซาฮาบูดิง กะดะแซ</v>
       </c>
       <c r="C3" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D3" t="str">
         <v>2565</v>
@@ -458,7 +458,7 @@
         <v>นายซุลกอรไนน์ เด็ง</v>
       </c>
       <c r="C4" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D4" t="str">
         <v>2565</v>
@@ -475,7 +475,7 @@
         <v>นายนัสรุดดีน ดอเลาะกาเดร์</v>
       </c>
       <c r="C5" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D5" t="str">
         <v>2565</v>
@@ -492,7 +492,7 @@
         <v>นายฟากีห์ สะอะเซ็ง</v>
       </c>
       <c r="C6" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D6" t="str">
         <v>2565</v>
@@ -509,7 +509,7 @@
         <v>นายเฟาร์ซาน ปะจู</v>
       </c>
       <c r="C7" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D7" t="str">
         <v>2565</v>
@@ -526,7 +526,7 @@
         <v>นายมุมิน บาสอสิดิก</v>
       </c>
       <c r="C8" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D8" t="str">
         <v>2565</v>
@@ -543,7 +543,7 @@
         <v>นายมูฮำหมัดฟิรดาวห์ เล็งฮะ</v>
       </c>
       <c r="C9" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D9" t="str">
         <v>2565</v>
@@ -560,7 +560,7 @@
         <v>นายลีเตอ เยอปอ</v>
       </c>
       <c r="C10" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D10" t="str">
         <v>2565</v>
@@ -577,7 +577,7 @@
         <v>นายอิคลาซ แวอาลี</v>
       </c>
       <c r="C11" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D11" t="str">
         <v>2565</v>
@@ -594,7 +594,7 @@
         <v>นายฮิลมีย์ บาฮา</v>
       </c>
       <c r="C12" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D12" t="str">
         <v>2565</v>
@@ -611,7 +611,7 @@
         <v>นายวัลลภ ตูหนะ</v>
       </c>
       <c r="C13" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D13" t="str">
         <v>2565</v>
@@ -628,7 +628,7 @@
         <v>นายปิยทัศน์ สำเร</v>
       </c>
       <c r="C14" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D14" t="str">
         <v>2565</v>
@@ -645,7 +645,7 @@
         <v>นางสาวกูซูวัยด๊ะ ลอนิ</v>
       </c>
       <c r="C15" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D15" t="str">
         <v>2565</v>
@@ -662,7 +662,7 @@
         <v>นางสาวนูรฮาน บากา</v>
       </c>
       <c r="C16" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D16" t="str">
         <v>2565</v>
@@ -679,7 +679,7 @@
         <v>นางสาวนูรุลฮูดา ลือบาน๊ะ</v>
       </c>
       <c r="C17" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D17" t="str">
         <v>2565</v>
@@ -696,7 +696,7 @@
         <v>นางสาวนูรูฮีซาน กา</v>
       </c>
       <c r="C18" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D18" t="str">
         <v>2565</v>
@@ -713,7 +713,7 @@
         <v>นางสาวฟาตียะห์ มะยุ</v>
       </c>
       <c r="C19" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D19" t="str">
         <v>2565</v>
@@ -730,7 +730,7 @@
         <v>นางสาวฟานูซ และสุบ</v>
       </c>
       <c r="C20" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D20" t="str">
         <v>2565</v>
@@ -747,7 +747,7 @@
         <v>นางสาวมณฑิตา ดาราโชติ</v>
       </c>
       <c r="C21" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D21" t="str">
         <v>2565</v>
@@ -764,7 +764,7 @@
         <v>นางสาวมุตมาอีนนะห์ เจ๊ะซอ</v>
       </c>
       <c r="C22" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D22" t="str">
         <v>2565</v>
@@ -781,7 +781,7 @@
         <v>นางสาวยัสมีน บาโง</v>
       </c>
       <c r="C23" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D23" t="str">
         <v>2565</v>
@@ -798,7 +798,7 @@
         <v>นางสาวรอยยาน ดอเลาะ</v>
       </c>
       <c r="C24" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D24" t="str">
         <v>2565</v>
@@ -815,7 +815,7 @@
         <v>นางสาวหัตญา สุดจิตร</v>
       </c>
       <c r="C25" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D25" t="str">
         <v>2565</v>
@@ -832,7 +832,7 @@
         <v>นางสาวอัซมาวีย์ วะเจดีย์</v>
       </c>
       <c r="C26" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D26" t="str">
         <v>2565</v>
@@ -849,7 +849,7 @@
         <v>นางสาวอัมนีย์ นือเร็ง</v>
       </c>
       <c r="C27" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D27" t="str">
         <v>2565</v>
@@ -866,7 +866,7 @@
         <v>นางสาวอัสมา กาซัน</v>
       </c>
       <c r="C28" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D28" t="str">
         <v>2565</v>
@@ -883,7 +883,7 @@
         <v>นางสาวอานีส อุมาร์</v>
       </c>
       <c r="C29" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D29" t="str">
         <v>2565</v>
@@ -900,7 +900,7 @@
         <v>นายฟาดิ้ล กาแลฮือมิ</v>
       </c>
       <c r="C30" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D30" t="str">
         <v>2565</v>
@@ -917,7 +917,7 @@
         <v>นายฟิรเดาส์ บินมิง</v>
       </c>
       <c r="C31" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D31" t="str">
         <v>2565</v>
@@ -934,7 +934,7 @@
         <v>นายฟุรกอน ดือราแม</v>
       </c>
       <c r="C32" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D32" t="str">
         <v>2565</v>
@@ -951,7 +951,7 @@
         <v>นายอัสรอฟ เจะเลง</v>
       </c>
       <c r="C33" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D33" t="str">
         <v>2565</v>
@@ -968,7 +968,7 @@
         <v>นายอีรฟาน สาเหาะ</v>
       </c>
       <c r="C34" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D34" t="str">
         <v>2565</v>
@@ -985,7 +985,7 @@
         <v>นางสาวคุนนัซ แสงประสพ</v>
       </c>
       <c r="C35" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D35" t="str">
         <v>2565</v>
@@ -1002,7 +1002,7 @@
         <v>นางสาวจันจิรา ผกามาศ</v>
       </c>
       <c r="C36" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D36" t="str">
         <v>2565</v>
@@ -1019,7 +1019,7 @@
         <v>นางสาวบัยญีนะห์ โตะโด</v>
       </c>
       <c r="C37" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D37" t="str">
         <v>2565</v>
@@ -1036,7 +1036,7 @@
         <v>นางสาวมุสลีมะห์ ตูแป</v>
       </c>
       <c r="C38" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D38" t="str">
         <v>2565</v>
@@ -1053,7 +1053,7 @@
         <v>นางสาวร็อยญาณ อาแว</v>
       </c>
       <c r="C39" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D39" t="str">
         <v>2565</v>
@@ -1070,7 +1070,7 @@
         <v>นางสาวลาตีฟะฮ์ ยูโซะ</v>
       </c>
       <c r="C40" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D40" t="str">
         <v>2565</v>
@@ -1087,7 +1087,7 @@
         <v>นางสาวเดียนา ลือแบซา</v>
       </c>
       <c r="C41" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D41" t="str">
         <v>2565</v>
@@ -1104,7 +1104,7 @@
         <v>นางสาวนาซู่ฮา เจะบู</v>
       </c>
       <c r="C42" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D42" t="str">
         <v>2565</v>
@@ -1121,7 +1121,7 @@
         <v>นางสาวซอลีฮา เจ๊ะเต๊ะ</v>
       </c>
       <c r="C43" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D43" t="str">
         <v>2565</v>
@@ -1138,7 +1138,7 @@
         <v>นางสาวซัรวา มูหิ</v>
       </c>
       <c r="C44" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D44" t="str">
         <v>2565</v>
@@ -1155,7 +1155,7 @@
         <v>นางสาวนุสนานี ตรอแซ</v>
       </c>
       <c r="C45" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D45" t="str">
         <v>2565</v>
@@ -1172,7 +1172,7 @@
         <v>นางสาวนูรุลฮูดา วี</v>
       </c>
       <c r="C46" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D46" t="str">
         <v>2565</v>
@@ -1189,7 +1189,7 @@
         <v>นางสาวนูร์เดียนา มะยูนุ</v>
       </c>
       <c r="C47" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D47" t="str">
         <v>2565</v>
@@ -1206,7 +1206,7 @@
         <v>นางสาวนูรอีมานี มามุ</v>
       </c>
       <c r="C48" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D48" t="str">
         <v>2565</v>
@@ -1223,7 +1223,7 @@
         <v>นางสาวนูรไอนี สามาแห</v>
       </c>
       <c r="C49" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D49" t="str">
         <v>2565</v>
@@ -1240,7 +1240,7 @@
         <v>นางสาวนูรีดา ยาโก๊ะ</v>
       </c>
       <c r="C50" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D50" t="str">
         <v>2565</v>
@@ -1257,7 +1257,7 @@
         <v>นางสาวบารออะฮ เจ๊ะมี</v>
       </c>
       <c r="C51" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D51" t="str">
         <v>2565</v>
@@ -1274,7 +1274,7 @@
         <v>นางสาวไมซาเราะห์ เจะมิง</v>
       </c>
       <c r="C52" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D52" t="str">
         <v>2565</v>
@@ -1291,7 +1291,7 @@
         <v>นางสาวยารอดะห์ บาราเฮง</v>
       </c>
       <c r="C53" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D53" t="str">
         <v>2565</v>
@@ -1308,7 +1308,7 @@
         <v>นางสาวสูไฮลา อาแว</v>
       </c>
       <c r="C54" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D54" t="str">
         <v>2565</v>
@@ -1325,7 +1325,7 @@
         <v>นางสาวอัฟนาน เจ๊ะสือแม</v>
       </c>
       <c r="C55" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D55" t="str">
         <v>2565</v>
@@ -1342,7 +1342,7 @@
         <v>นางสาวอัฟฟาฟ เจ๊ะเต๊ะ</v>
       </c>
       <c r="C56" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D56" t="str">
         <v>2565</v>
@@ -1359,7 +1359,7 @@
         <v>นางสาวอารีนี เจาะกลาดี</v>
       </c>
       <c r="C57" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D57" t="str">
         <v>2565</v>
@@ -1376,7 +1376,7 @@
         <v>นางสาวโนรอามีนีย์ หะยีดิง</v>
       </c>
       <c r="C58" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D58" t="str">
         <v>2565</v>
@@ -1393,7 +1393,7 @@
         <v>นางสาวมุสลีฮา มูเซะ</v>
       </c>
       <c r="C59" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D59" t="str">
         <v>2565</v>
@@ -1410,7 +1410,7 @@
         <v>นางสาวมูนา ดาฮะกา</v>
       </c>
       <c r="C60" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D60" t="str">
         <v>2565</v>
@@ -1427,7 +1427,7 @@
         <v>นางสาวซีฟาอ์ มามะ</v>
       </c>
       <c r="C61" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D61" t="str">
         <v>2565</v>
@@ -1444,7 +1444,7 @@
         <v>นายซอลีฮีน ฮะอุรา</v>
       </c>
       <c r="C62" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D62" t="str">
         <v>2565</v>
@@ -1461,7 +1461,7 @@
         <v>นายฟาดิลล์ มามะ</v>
       </c>
       <c r="C63" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D63" t="str">
         <v>2565</v>
@@ -1478,7 +1478,7 @@
         <v>นายมุสลิม ยูโซะ</v>
       </c>
       <c r="C64" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D64" t="str">
         <v>2565</v>
@@ -1495,7 +1495,7 @@
         <v>นายวาอิล บาฮา</v>
       </c>
       <c r="C65" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D65" t="str">
         <v>2565</v>
@@ -1512,7 +1512,7 @@
         <v>นายอันวา เตะการี</v>
       </c>
       <c r="C66" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D66" t="str">
         <v>2565</v>
@@ -1529,7 +1529,7 @@
         <v>นายอัมฟาล สาริปา</v>
       </c>
       <c r="C67" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D67" t="str">
         <v>2565</v>
@@ -1546,7 +1546,7 @@
         <v>นายอัศรอม แหม๊ะ</v>
       </c>
       <c r="C68" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D68" t="str">
         <v>2565</v>
@@ -1563,7 +1563,7 @@
         <v>นายอาแซ สะมะแอลีมา</v>
       </c>
       <c r="C69" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D69" t="str">
         <v>2565</v>
@@ -1580,7 +1580,7 @@
         <v>นายอารฟัน เดรส</v>
       </c>
       <c r="C70" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D70" t="str">
         <v>2565</v>
@@ -1597,7 +1597,7 @@
         <v>นายอากิฟ แซการี</v>
       </c>
       <c r="C71" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D71" t="str">
         <v>2565</v>
@@ -1614,7 +1614,7 @@
         <v>นางสาวฟิตรียะห์ ลาเตะ</v>
       </c>
       <c r="C72" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D72" t="str">
         <v>2565</v>
@@ -1631,7 +1631,7 @@
         <v>นางสาวค็อยรีณี กาเซ็ง</v>
       </c>
       <c r="C73" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D73" t="str">
         <v>2565</v>
@@ -1648,7 +1648,7 @@
         <v>นางสาวจีรภรณ์ เล็กกุล</v>
       </c>
       <c r="C74" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D74" t="str">
         <v>2565</v>
@@ -1665,7 +1665,7 @@
         <v>นางสาวซอลีฮะห์ กาโฮง</v>
       </c>
       <c r="C75" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D75" t="str">
         <v>2565</v>
@@ -1682,7 +1682,7 @@
         <v>นางสาวซอลีฮะห์ ลาเต๊ะ</v>
       </c>
       <c r="C76" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D76" t="str">
         <v>2565</v>
@@ -1699,7 +1699,7 @@
         <v>นางสาวซัรฟาอ์ เจ๊ะลง</v>
       </c>
       <c r="C77" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D77" t="str">
         <v>2565</v>
@@ -1716,7 +1716,7 @@
         <v>นางสาวซีตีอาอีเซ๊าะ ยีหะมะ</v>
       </c>
       <c r="C78" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D78" t="str">
         <v>2565</v>
@@ -1733,7 +1733,7 @@
         <v>นางสาวซูมัยยะห์ เจะมะ</v>
       </c>
       <c r="C79" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D79" t="str">
         <v>2565</v>
@@ -1750,7 +1750,7 @@
         <v>นางสาวญูไวดี โต๊ะสกุล</v>
       </c>
       <c r="C80" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D80" t="str">
         <v>2565</v>
@@ -1767,7 +1767,7 @@
         <v>นางสาวณีฮาล วาเตะ</v>
       </c>
       <c r="C81" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D81" t="str">
         <v>2565</v>
@@ -1784,7 +1784,7 @@
         <v>นางสาวเดียนา วาหะ</v>
       </c>
       <c r="C82" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D82" t="str">
         <v>2565</v>
@@ -1801,7 +1801,7 @@
         <v>นางสาวต่วนนีฟาน บรึดู</v>
       </c>
       <c r="C83" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D83" t="str">
         <v>2565</v>
@@ -1818,7 +1818,7 @@
         <v>นางสาวตัสกีน หมะเต๊ะ</v>
       </c>
       <c r="C84" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D84" t="str">
         <v>2565</v>
@@ -1835,7 +1835,7 @@
         <v>นางสาวนัสนีน ตะวัน</v>
       </c>
       <c r="C85" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D85" t="str">
         <v>2565</v>
@@ -1852,7 +1852,7 @@
         <v>นางสาวนัสรียะห์ อีแต</v>
       </c>
       <c r="C86" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D86" t="str">
         <v>2565</v>
@@ -1869,7 +1869,7 @@
         <v>นางสาวนาซอฟะห์ ดอคอ</v>
       </c>
       <c r="C87" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D87" t="str">
         <v>2565</v>
@@ -1886,7 +1886,7 @@
         <v>นางสาวนาเดีย บินรัตแก้ว</v>
       </c>
       <c r="C88" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D88" t="str">
         <v>2565</v>
@@ -1903,7 +1903,7 @@
         <v>นางสาวซูไฮลา ยามูสะนอ</v>
       </c>
       <c r="C89" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D89" t="str">
         <v>2565</v>
@@ -1920,7 +1920,7 @@
         <v>นางสาวนิอานิส สาแม</v>
       </c>
       <c r="C90" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D90" t="str">
         <v>2565</v>
@@ -1937,7 +1937,7 @@
         <v>นางสาวนุรฟาน ลอเด็ง</v>
       </c>
       <c r="C91" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D91" t="str">
         <v>2565</v>
@@ -1954,7 +1954,7 @@
         <v>นางสาวนุรอัยณี อุมา</v>
       </c>
       <c r="C92" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D92" t="str">
         <v>2565</v>
@@ -1971,7 +1971,7 @@
         <v>นางสาวนุรอีมาน มามะ</v>
       </c>
       <c r="C93" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D93" t="str">
         <v>2565</v>
@@ -1988,7 +1988,7 @@
         <v>นางสาวนูรมา กาเจร์</v>
       </c>
       <c r="C94" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D94" t="str">
         <v>2565</v>
@@ -2005,7 +2005,7 @@
         <v>นางสาวนูรอัฟนาน เบญดาโอะ</v>
       </c>
       <c r="C95" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D95" t="str">
         <v>2565</v>
@@ -2022,7 +2022,7 @@
         <v>นางสาวนูรอัย แมดง</v>
       </c>
       <c r="C96" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D96" t="str">
         <v>2565</v>
@@ -2039,7 +2039,7 @@
         <v>นางสาวนูรอัยนี สะมะแอ</v>
       </c>
       <c r="C97" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D97" t="str">
         <v>2565</v>
@@ -2056,7 +2056,7 @@
         <v>นางสาวนูรอารีนา อาหลี</v>
       </c>
       <c r="C98" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D98" t="str">
         <v>2565</v>
@@ -2073,7 +2073,7 @@
         <v>นางสาวนูรฮายาตี แมดิงแว</v>
       </c>
       <c r="C99" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D99" t="str">
         <v>2565</v>
@@ -2090,7 +2090,7 @@
         <v>นางสาวนูรีฮะ หล๊ะตำ</v>
       </c>
       <c r="C100" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D100" t="str">
         <v>2565</v>
@@ -2107,7 +2107,7 @@
         <v>นางสาวนูรูลอีมาน ซีเด๊ะ</v>
       </c>
       <c r="C101" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D101" t="str">
         <v>2565</v>
@@ -2124,7 +2124,7 @@
         <v>นางสาวฟาตีเมาะห์ บาเน็ง</v>
       </c>
       <c r="C102" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D102" t="str">
         <v>2565</v>
@@ -2141,7 +2141,7 @@
         <v>นางสาวมาดีฮะห์ แมเร๊าะ</v>
       </c>
       <c r="C103" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D103" t="str">
         <v>2565</v>
@@ -2158,7 +2158,7 @@
         <v>นางสาวมุสลีมะห์ วาแฮ</v>
       </c>
       <c r="C104" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D104" t="str">
         <v>2565</v>
@@ -2175,7 +2175,7 @@
         <v>นางสาวมูนาดา ดอปอ</v>
       </c>
       <c r="C105" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D105" t="str">
         <v>2565</v>
@@ -2192,7 +2192,7 @@
         <v>นางสาวยัรมี ยีสาอิ</v>
       </c>
       <c r="C106" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D106" t="str">
         <v>2565</v>
@@ -2209,7 +2209,7 @@
         <v>นางสาวยัสมิน สาเอะ</v>
       </c>
       <c r="C107" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D107" t="str">
         <v>2565</v>
@@ -2226,7 +2226,7 @@
         <v>นางสาวยาวารี เหะซา</v>
       </c>
       <c r="C108" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D108" t="str">
         <v>2565</v>
@@ -2243,7 +2243,7 @@
         <v>นางสาวรอฮานี สะมะแอ</v>
       </c>
       <c r="C109" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D109" t="str">
         <v>2565</v>
@@ -2260,7 +2260,7 @@
         <v>นางสาวรุสมี แช่มช้อย</v>
       </c>
       <c r="C110" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D110" t="str">
         <v>2565</v>
@@ -2277,7 +2277,7 @@
         <v>นางสาวลาตีฟาห์ ดาราแม็ง</v>
       </c>
       <c r="C111" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D111" t="str">
         <v>2565</v>
@@ -2294,7 +2294,7 @@
         <v>นางสาววีอาร์ม วานิ</v>
       </c>
       <c r="C112" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D112" t="str">
         <v>2565</v>
@@ -2311,7 +2311,7 @@
         <v>นางสาวศศิภา หวังหล้า</v>
       </c>
       <c r="C113" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D113" t="str">
         <v>2565</v>
@@ -2328,7 +2328,7 @@
         <v>นางสาวศิริญญา ลูกเด็น</v>
       </c>
       <c r="C114" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D114" t="str">
         <v>2565</v>
@@ -2345,7 +2345,7 @@
         <v>นางสาวศิรินญา ปานคู</v>
       </c>
       <c r="C115" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D115" t="str">
         <v>2565</v>
@@ -2362,7 +2362,7 @@
         <v>นางสาวสุฟียานี มาหะมะ</v>
       </c>
       <c r="C116" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D116" t="str">
         <v>2565</v>
@@ -2379,7 +2379,7 @@
         <v>นางสาวสุรียานี เจ๊ะสือเเม</v>
       </c>
       <c r="C117" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D117" t="str">
         <v>2565</v>
@@ -2396,7 +2396,7 @@
         <v>นางสาวอมีนี แวตีซา</v>
       </c>
       <c r="C118" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D118" t="str">
         <v>2565</v>
@@ -2413,7 +2413,7 @@
         <v>นางสาวอันวารี มัจฉาเวช</v>
       </c>
       <c r="C119" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D119" t="str">
         <v>2565</v>
@@ -2430,7 +2430,7 @@
         <v>นางสาวอาดีละห์ แบเล๊าะ</v>
       </c>
       <c r="C120" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D120" t="str">
         <v>2565</v>
@@ -2447,7 +2447,7 @@
         <v>นางสาวอามาลีนา มะลี</v>
       </c>
       <c r="C121" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D121" t="str">
         <v>2565</v>
@@ -2464,7 +2464,7 @@
         <v>นางสาวอารอฟะห์ อับดุลลาเต๊ะ</v>
       </c>
       <c r="C122" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D122" t="str">
         <v>2565</v>
@@ -2481,7 +2481,7 @@
         <v>นางสาวอาอิฉะฮ์ หม่าหลี</v>
       </c>
       <c r="C123" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D123" t="str">
         <v>2565</v>
@@ -2498,7 +2498,7 @@
         <v>นางสาวอีมาน เบ็ญยานุสรณ์</v>
       </c>
       <c r="C124" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D124" t="str">
         <v>2565</v>
@@ -2515,7 +2515,7 @@
         <v>นางสาวฮัสมีรา กาเซ็ง</v>
       </c>
       <c r="C125" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D125" t="str">
         <v>2565</v>
@@ -2532,7 +2532,7 @@
         <v>นางสาวฮาฟีเซาะห์ มะ</v>
       </c>
       <c r="C126" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D126" t="str">
         <v>2565</v>
@@ -2549,7 +2549,7 @@
         <v>นางสาวฮาวีซะห์ เวาะเย็ง</v>
       </c>
       <c r="C127" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D127" t="str">
         <v>2565</v>
@@ -2566,7 +2566,7 @@
         <v>นางสาวฮูรุนอีน กาเจ</v>
       </c>
       <c r="C128" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D128" t="str">
         <v>2565</v>
@@ -2583,7 +2583,7 @@
         <v>นางสาวดารีย๊ะ เลาะราแม</v>
       </c>
       <c r="C129" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D129" t="str">
         <v>2565</v>
@@ -2600,7 +2600,7 @@
         <v>นางสาวฮาซานะห์ ดอเลาะ</v>
       </c>
       <c r="C130" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D130" t="str">
         <v>2565</v>
@@ -2617,7 +2617,7 @@
         <v>นางสาวโซเฟีย ดือราแม</v>
       </c>
       <c r="C131" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D131" t="str">
         <v>2565</v>
@@ -2634,7 +2634,7 @@
         <v>นางสาวฟิรดาวซ เจ๊ะเฮง</v>
       </c>
       <c r="C132" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D132" t="str">
         <v>2565</v>
@@ -2651,7 +2651,7 @@
         <v>นางสาวมินดา สะบาย</v>
       </c>
       <c r="C133" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D133" t="str">
         <v>2565</v>
@@ -2668,7 +2668,7 @@
         <v>นางสาวอาฟานีน สะตา</v>
       </c>
       <c r="C134" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D134" t="str">
         <v>2565</v>
@@ -2685,7 +2685,7 @@
         <v>นางสาวอัสนา ยายอ</v>
       </c>
       <c r="C135" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D135" t="str">
         <v>2565</v>
@@ -2702,7 +2702,7 @@
         <v>นางสาวอิฮซาน แดมะ</v>
       </c>
       <c r="C136" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D136" t="str">
         <v>2565</v>
@@ -2719,7 +2719,7 @@
         <v>นางสาวคริสมาส ทองประทุม</v>
       </c>
       <c r="C137" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D137" t="str">
         <v>2565</v>
@@ -2736,7 +2736,7 @@
         <v>นางสาวนูรีดา ลือแบซา</v>
       </c>
       <c r="C138" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D138" t="str">
         <v>2565</v>
@@ -2753,7 +2753,7 @@
         <v>นางสาวคอรีเย๊าะ การูมอ</v>
       </c>
       <c r="C139" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D139" t="str">
         <v>2565</v>
@@ -2770,7 +2770,7 @@
         <v>นายวาริซ ลีลานนท์</v>
       </c>
       <c r="C140" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D140" t="str">
         <v>2565</v>
@@ -2787,7 +2787,7 @@
         <v>นางสาวคอรีเย๊าะ หะแมะลี</v>
       </c>
       <c r="C141" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D141" t="str">
         <v>2565</v>
@@ -2804,7 +2804,7 @@
         <v>นางสาวเคาละห์ แม</v>
       </c>
       <c r="C142" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D142" t="str">
         <v>2565</v>
@@ -2821,7 +2821,7 @@
         <v>นางสาวชามีมี อีตำ</v>
       </c>
       <c r="C143" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D143" t="str">
         <v>2565</v>
@@ -2838,7 +2838,7 @@
         <v>นางสาวซอลีฮะห์ สูหลง</v>
       </c>
       <c r="C144" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D144" t="str">
         <v>2565</v>
@@ -2855,7 +2855,7 @@
         <v>นางสาวซัลซาบีน สาและ</v>
       </c>
       <c r="C145" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D145" t="str">
         <v>2565</v>
@@ -2872,7 +2872,7 @@
         <v>นางสาวซาฮีดะห์ หะยีกอเดร์</v>
       </c>
       <c r="C146" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D146" t="str">
         <v>2565</v>
@@ -2889,7 +2889,7 @@
         <v>นางสาวซูณีตา สุหลง</v>
       </c>
       <c r="C147" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D147" t="str">
         <v>2565</v>
@@ -2906,7 +2906,7 @@
         <v>นางสาวซูรัยดา เจ๊ะเล๊าะ</v>
       </c>
       <c r="C148" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D148" t="str">
         <v>2565</v>
@@ -2923,7 +2923,7 @@
         <v>นางสาวโซเฟีย ยุโซะ</v>
       </c>
       <c r="C149" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D149" t="str">
         <v>2565</v>
@@ -2940,7 +2940,7 @@
         <v>นางสาวโซเฟีย กาเร็ง</v>
       </c>
       <c r="C150" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D150" t="str">
         <v>2565</v>
@@ -2957,7 +2957,7 @@
         <v>นางสาวญัสมีน ลือแบซา</v>
       </c>
       <c r="C151" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D151" t="str">
         <v>2565</v>
@@ -2974,7 +2974,7 @@
         <v>นางสาวณูรีน มิสลิมิน</v>
       </c>
       <c r="C152" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D152" t="str">
         <v>2565</v>
@@ -2991,7 +2991,7 @@
         <v>นางสาวตัซนีม คอลอราแม</v>
       </c>
       <c r="C153" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D153" t="str">
         <v>2565</v>
@@ -3008,7 +3008,7 @@
         <v>นางสาวตัสนีม เลาะสุหลง</v>
       </c>
       <c r="C154" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D154" t="str">
         <v>2565</v>
@@ -3025,7 +3025,7 @@
         <v>นางสาวตัสมีนี อาแซ</v>
       </c>
       <c r="C155" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D155" t="str">
         <v>2565</v>
@@ -3042,7 +3042,7 @@
         <v>นางสาวธาลินี หมะปิ</v>
       </c>
       <c r="C156" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D156" t="str">
         <v>2565</v>
@@ -3059,7 +3059,7 @@
         <v>นางสาวนดา เสลา</v>
       </c>
       <c r="C157" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D157" t="str">
         <v>2565</v>
@@ -3076,7 +3076,7 @@
         <v>นางสาวนะดา อุสมา</v>
       </c>
       <c r="C158" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D158" t="str">
         <v>2565</v>
@@ -3093,7 +3093,7 @@
         <v>นางสาวนัสรีน บือราเฮง</v>
       </c>
       <c r="C159" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D159" t="str">
         <v>2565</v>
@@ -3110,7 +3110,7 @@
         <v>นางสาวนัสรีน เจ๊ะอาลี</v>
       </c>
       <c r="C160" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D160" t="str">
         <v>2565</v>
@@ -3127,7 +3127,7 @@
         <v>นางสาวนาซีฟะห์ ตาบา</v>
       </c>
       <c r="C161" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D161" t="str">
         <v>2565</v>
@@ -3144,7 +3144,7 @@
         <v>นางสาวนาซูฮา มูซอ</v>
       </c>
       <c r="C162" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D162" t="str">
         <v>2565</v>
@@ -3161,7 +3161,7 @@
         <v>นางสาวนาฟีละห์ เจ๊ะอารงค์</v>
       </c>
       <c r="C163" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D163" t="str">
         <v>2565</v>
@@ -3178,7 +3178,7 @@
         <v>นางสาวนาอีมะห์ สาและ</v>
       </c>
       <c r="C164" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D164" t="str">
         <v>2565</v>
@@ -3195,7 +3195,7 @@
         <v>นางสาวนาอีมะห์ จูเฮง</v>
       </c>
       <c r="C165" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D165" t="str">
         <v>2565</v>
@@ -3212,7 +3212,7 @@
         <v>นางสาวนิซูไวบะห์ นิโซะ</v>
       </c>
       <c r="C166" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D166" t="str">
         <v>2565</v>
@@ -3229,7 +3229,7 @@
         <v>นางสาวนิมาดูรา เจะซู</v>
       </c>
       <c r="C167" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D167" t="str">
         <v>2565</v>
@@ -3246,7 +3246,7 @@
         <v>นางสาวนุรมี กะโด</v>
       </c>
       <c r="C168" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D168" t="str">
         <v>2565</v>
@@ -3263,7 +3263,7 @@
         <v>นางสาวนุรไมซูรา เจะแห</v>
       </c>
       <c r="C169" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D169" t="str">
         <v>2565</v>
@@ -3280,7 +3280,7 @@
         <v>นางสาวนูรฟาฏิณี เจะบู</v>
       </c>
       <c r="C170" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D170" t="str">
         <v>2565</v>
@@ -3297,7 +3297,7 @@
         <v>นางสาวนูรฟาตีฮะห์ ดอเล๊าะ</v>
       </c>
       <c r="C171" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D171" t="str">
         <v>2565</v>
@@ -3314,7 +3314,7 @@
         <v>นางสาวนูรฟารีซา ดือราซอ</v>
       </c>
       <c r="C172" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D172" t="str">
         <v>2565</v>
@@ -3331,7 +3331,7 @@
         <v>นางสาวนูรมาณีย์ ดอปิ</v>
       </c>
       <c r="C173" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D173" t="str">
         <v>2565</v>
@@ -3348,7 +3348,7 @@
         <v>นางสาวนูรมี ยูโซะ</v>
       </c>
       <c r="C174" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D174" t="str">
         <v>2565</v>
@@ -3365,7 +3365,7 @@
         <v>นางสาวนัรมีน ดาโตะ</v>
       </c>
       <c r="C175" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D175" t="str">
         <v>2565</v>
@@ -3382,7 +3382,7 @@
         <v>นางสาวนูรอิมฏีซาน มะเก๊ะ</v>
       </c>
       <c r="C176" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D176" t="str">
         <v>2565</v>
@@ -3399,7 +3399,7 @@
         <v>นางสาวนูรไอนี แกะซิ</v>
       </c>
       <c r="C177" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D177" t="str">
         <v>2565</v>
@@ -3416,7 +3416,7 @@
         <v>นางสาวนูรฮาซีกีน โต๊ะเล๊าะ</v>
       </c>
       <c r="C178" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D178" t="str">
         <v>2565</v>
@@ -3433,7 +3433,7 @@
         <v>นางสาวนูรฮาฟานี อูเซ็ง</v>
       </c>
       <c r="C179" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D179" t="str">
         <v>2565</v>
@@ -3450,7 +3450,7 @@
         <v>นางสาวนูรฮาฟีลีน วาดิง</v>
       </c>
       <c r="C180" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D180" t="str">
         <v>2565</v>
@@ -3467,7 +3467,7 @@
         <v>นางสาวนูรีซัน เจ๊ะเละ</v>
       </c>
       <c r="C181" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D181" t="str">
         <v>2565</v>
@@ -3484,7 +3484,7 @@
         <v>นางสาวนูรีซัน เจะแต</v>
       </c>
       <c r="C182" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D182" t="str">
         <v>2565</v>
@@ -3501,7 +3501,7 @@
         <v>นางสาวนูรีดา หมาดงะ</v>
       </c>
       <c r="C183" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D183" t="str">
         <v>2565</v>
@@ -3518,7 +3518,7 @@
         <v>นางสาวนูรุลบายาน ดือราแม</v>
       </c>
       <c r="C184" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D184" t="str">
         <v>2565</v>
@@ -3535,7 +3535,7 @@
         <v>นางสาวโนรฟาซีลา สอและ</v>
       </c>
       <c r="C185" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D185" t="str">
         <v>2565</v>
@@ -3552,7 +3552,7 @@
         <v>นางสาวบูทุม มาเยอะ</v>
       </c>
       <c r="C186" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D186" t="str">
         <v>2565</v>
@@ -3569,7 +3569,7 @@
         <v>นางสาวผัลย์ศุภา วาโซ๊ะ</v>
       </c>
       <c r="C187" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D187" t="str">
         <v>2565</v>
@@ -3586,7 +3586,7 @@
         <v>นางสาวพธิญา หยีมะเหร็ม</v>
       </c>
       <c r="C188" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D188" t="str">
         <v>2565</v>
@@ -3603,7 +3603,7 @@
         <v>นางสาวฟะฎียะห์ มะเด็ง</v>
       </c>
       <c r="C189" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D189" t="str">
         <v>2565</v>
@@ -3620,7 +3620,7 @@
         <v>นางสาวฟัจญรียะห์ คงเดิม</v>
       </c>
       <c r="C190" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D190" t="str">
         <v>2565</v>
@@ -3637,7 +3637,7 @@
         <v>นางสาวฟาฏินา หวันบวช</v>
       </c>
       <c r="C191" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D191" t="str">
         <v>2565</v>
@@ -3654,7 +3654,7 @@
         <v>นางสาวฟาดีละห์ กาซง</v>
       </c>
       <c r="C192" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D192" t="str">
         <v>2565</v>
@@ -3671,7 +3671,7 @@
         <v>นางสาวฟาดีลา นิจะ</v>
       </c>
       <c r="C193" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D193" t="str">
         <v>2565</v>
@@ -3688,7 +3688,7 @@
         <v>นางสาวฟาดีลา กาเต๊ะ</v>
       </c>
       <c r="C194" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D194" t="str">
         <v>2565</v>
@@ -3705,7 +3705,7 @@
         <v>นางสาวฟาติน ซามอ</v>
       </c>
       <c r="C195" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D195" t="str">
         <v>2565</v>
@@ -3722,7 +3722,7 @@
         <v>นางสาวฟาตีน กือลาแต</v>
       </c>
       <c r="C196" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D196" t="str">
         <v>2565</v>
@@ -3739,7 +3739,7 @@
         <v>นางสาวฟาตีฮะห์ มะดีเยาะ</v>
       </c>
       <c r="C197" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D197" t="str">
         <v>2565</v>
@@ -3756,7 +3756,7 @@
         <v>นางสาวฟิตตรี กะดอง</v>
       </c>
       <c r="C198" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D198" t="str">
         <v>2565</v>
@@ -3773,7 +3773,7 @@
         <v>นางสาวฟิตรี โฮมียอ</v>
       </c>
       <c r="C199" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D199" t="str">
         <v>2565</v>
@@ -3790,7 +3790,7 @@
         <v>นางสาวฟิตเราะ สือรี</v>
       </c>
       <c r="C200" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D200" t="str">
         <v>2565</v>
@@ -3807,7 +3807,7 @@
         <v>นางสาวฟิตเราะห์ สาเเละ</v>
       </c>
       <c r="C201" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D201" t="str">
         <v>2565</v>
@@ -3824,7 +3824,7 @@
         <v>นางสาวมันนาน มะหลี</v>
       </c>
       <c r="C202" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D202" t="str">
         <v>2565</v>
@@ -3841,7 +3841,7 @@
         <v>นางสาวมัสตูรา วาเซ็ง</v>
       </c>
       <c r="C203" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D203" t="str">
         <v>2565</v>
@@ -3858,7 +3858,7 @@
         <v>นางสาวมาริษา เจ๊ะบากา</v>
       </c>
       <c r="C204" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D204" t="str">
         <v>2565</v>
@@ -3875,7 +3875,7 @@
         <v>นางสาวไมนี โดมะแซ</v>
       </c>
       <c r="C205" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D205" t="str">
         <v>2565</v>
@@ -3892,7 +3892,7 @@
         <v>นางสาวรัตนวลี สระทองอยู่</v>
       </c>
       <c r="C206" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D206" t="str">
         <v>2565</v>
@@ -3909,7 +3909,7 @@
         <v>นางสาวรินลณา สาระภี</v>
       </c>
       <c r="C207" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D207" t="str">
         <v>2565</v>
@@ -3926,7 +3926,7 @@
         <v>นางสาววรัญญา ภัยชำนาญ</v>
       </c>
       <c r="C208" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D208" t="str">
         <v>2565</v>
@@ -3943,7 +3943,7 @@
         <v>นางสาววัณนูรูลนัจมี แวอาลี</v>
       </c>
       <c r="C209" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D209" t="str">
         <v>2565</v>
@@ -3960,7 +3960,7 @@
         <v>นางสาววิลดาน หมุสอ</v>
       </c>
       <c r="C210" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D210" t="str">
         <v>2565</v>
@@ -3977,7 +3977,7 @@
         <v>นางสาวสารีณา โตะกอแล</v>
       </c>
       <c r="C211" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D211" t="str">
         <v>2565</v>
@@ -3994,7 +3994,7 @@
         <v>นางสาวสุวัยบะห์ อีแต</v>
       </c>
       <c r="C212" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D212" t="str">
         <v>2565</v>
@@ -4011,7 +4011,7 @@
         <v>นางสาวอชิรญาณ์ แหละเหย็บ</v>
       </c>
       <c r="C213" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D213" t="str">
         <v>2565</v>
@@ -4028,7 +4028,7 @@
         <v>นางสาวอริสา โตแก้ว</v>
       </c>
       <c r="C214" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D214" t="str">
         <v>2565</v>
@@ -4045,7 +4045,7 @@
         <v>นางสาวอัฟนาน กลาแต</v>
       </c>
       <c r="C215" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D215" t="str">
         <v>2565</v>
@@ -4062,7 +4062,7 @@
         <v>นางสาวอาซานี ซิบากา</v>
       </c>
       <c r="C216" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D216" t="str">
         <v>2565</v>
@@ -4079,7 +4079,7 @@
         <v>นางสาวอานิส สะมะแอ</v>
       </c>
       <c r="C217" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D217" t="str">
         <v>2565</v>
@@ -4096,7 +4096,7 @@
         <v>นางสาวอามานีนา เชตเตอร์โมฮามัด</v>
       </c>
       <c r="C218" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D218" t="str">
         <v>2565</v>
@@ -4113,7 +4113,7 @@
         <v>นางสาวอิบตีซาม โต๊ะลง</v>
       </c>
       <c r="C219" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D219" t="str">
         <v>2565</v>
@@ -4130,7 +4130,7 @@
         <v>นางสาวอิลฮามี อาหามะ</v>
       </c>
       <c r="C220" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D220" t="str">
         <v>2565</v>
@@ -4147,7 +4147,7 @@
         <v>นางสาวฮัยดัร มะเกะ</v>
       </c>
       <c r="C221" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D221" t="str">
         <v>2565</v>
@@ -4164,7 +4164,7 @@
         <v>นางสาวฮัยดา มะเกะ</v>
       </c>
       <c r="C222" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D222" t="str">
         <v>2565</v>
@@ -4181,7 +4181,7 @@
         <v>นางสาวฮัลวาตี สาแม</v>
       </c>
       <c r="C223" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D223" t="str">
         <v>2565</v>
@@ -4198,7 +4198,7 @@
         <v>นางสาวฮานีซะห์ บือเเน</v>
       </c>
       <c r="C224" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D224" t="str">
         <v>2565</v>
@@ -4215,7 +4215,7 @@
         <v>นางสาวฮานีซา เจ๊ะมะเจ</v>
       </c>
       <c r="C225" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D225" t="str">
         <v>2565</v>
@@ -4232,7 +4232,7 @@
         <v>นางสาวฮานีฟ ซง</v>
       </c>
       <c r="C226" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D226" t="str">
         <v>2565</v>
@@ -4249,7 +4249,7 @@
         <v>นางสาวฮีดายะห์ สะเตาะ</v>
       </c>
       <c r="C227" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D227" t="str">
         <v>2565</v>
@@ -4266,7 +4266,7 @@
         <v>นางสาวซูไมละห์ มะเก๊ะ</v>
       </c>
       <c r="C228" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D228" t="str">
         <v>2565</v>
@@ -4283,7 +4283,7 @@
         <v>นางสาวอานีซา สะตำ</v>
       </c>
       <c r="C229" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D229" t="str">
         <v>2565</v>
@@ -4300,7 +4300,7 @@
         <v>นางสาววีอาร์ม วานิ</v>
       </c>
       <c r="C230" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D230" t="str">
         <v>2565</v>
@@ -4317,7 +4317,7 @@
         <v>นางสาวซาตีบี หะยีสาแม็ง</v>
       </c>
       <c r="C231" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>เคมี</v>
       </c>
       <c r="D231" t="str">
         <v>2565</v>
@@ -4334,7 +4334,7 @@
         <v>นางสาวซีฟาอ์ มามะ</v>
       </c>
       <c r="C232" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>เคมี</v>
       </c>
       <c r="D232" t="str">
         <v>2565</v>
@@ -4351,7 +4351,7 @@
         <v>นางสาวร็อยมีย์ สูแน</v>
       </c>
       <c r="C233" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>เคมี</v>
       </c>
       <c r="D233" t="str">
         <v>2565</v>
@@ -4368,7 +4368,7 @@
         <v>นางสาวกูนาเดีย รายอเง๊าะ</v>
       </c>
       <c r="C234" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>เคมี</v>
       </c>
       <c r="D234" t="str">
         <v>2565</v>
@@ -4385,7 +4385,7 @@
         <v>นายมุศลิฮ เจ๊ะซู</v>
       </c>
       <c r="C235" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D235" t="str">
         <v>2566</v>
@@ -4402,7 +4402,7 @@
         <v>นางสาวกัรตีนี เวาะโด</v>
       </c>
       <c r="C236" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D236" t="str">
         <v>2566</v>
@@ -4419,7 +4419,7 @@
         <v>นางสาวคอยรุนนีซาอ์ มะเยาะ</v>
       </c>
       <c r="C237" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D237" t="str">
         <v>2566</v>
@@ -4436,7 +4436,7 @@
         <v>นางสาวเจะวัรดะห์ เจะมามะ</v>
       </c>
       <c r="C238" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D238" t="str">
         <v>2566</v>
@@ -4453,7 +4453,7 @@
         <v>นางสาวชลธิชา โต๊ะเส็น</v>
       </c>
       <c r="C239" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D239" t="str">
         <v>2566</v>
@@ -4470,7 +4470,7 @@
         <v>นางสาวชีฟาอ์ เจ๊ะโด</v>
       </c>
       <c r="C240" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D240" t="str">
         <v>2566</v>
@@ -4487,7 +4487,7 @@
         <v>นางสาวซอรีฮะ เจะกอเดร์</v>
       </c>
       <c r="C241" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D241" t="str">
         <v>2566</v>
@@ -4504,7 +4504,7 @@
         <v>นางสาวซามีฮะห์ ดือเร๊ะ</v>
       </c>
       <c r="C242" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D242" t="str">
         <v>2566</v>
@@ -4521,7 +4521,7 @@
         <v>นางสาวซุลฟา มูดอ</v>
       </c>
       <c r="C243" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D243" t="str">
         <v>2566</v>
@@ -4538,7 +4538,7 @@
         <v>นางสาวซูวัยบะห์ เซ็ง</v>
       </c>
       <c r="C244" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D244" t="str">
         <v>2566</v>
@@ -4555,7 +4555,7 @@
         <v>นางสาวนัจญ์วา แวและ</v>
       </c>
       <c r="C245" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D245" t="str">
         <v>2566</v>
@@ -4572,7 +4572,7 @@
         <v>นางสาวณภัทร สันตะกิจ</v>
       </c>
       <c r="C246" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D246" t="str">
         <v>2566</v>
@@ -4589,7 +4589,7 @@
         <v>นางสาวณัชชา สาม่าน</v>
       </c>
       <c r="C247" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D247" t="str">
         <v>2566</v>
@@ -4606,7 +4606,7 @@
         <v>นางสาวณัชมีย์ มูซอ</v>
       </c>
       <c r="C248" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D248" t="str">
         <v>2566</v>
@@ -4623,7 +4623,7 @@
         <v>นางสาวตักวา กาเอะ</v>
       </c>
       <c r="C249" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D249" t="str">
         <v>2566</v>
@@ -4640,7 +4640,7 @@
         <v>นางสาวตักวา ดาหมาด</v>
       </c>
       <c r="C250" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D250" t="str">
         <v>2566</v>
@@ -4657,7 +4657,7 @@
         <v>นางสาวตักวา ดอเล๊าะ</v>
       </c>
       <c r="C251" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D251" t="str">
         <v>2566</v>
@@ -4674,7 +4674,7 @@
         <v>นางสาวตัสนีม ยุทธแสง</v>
       </c>
       <c r="C252" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D252" t="str">
         <v>2566</v>
@@ -4691,7 +4691,7 @@
         <v>นางสาวตัสนีม แต</v>
       </c>
       <c r="C253" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D253" t="str">
         <v>2566</v>
@@ -4708,7 +4708,7 @@
         <v>นางสาวนัจวา ยาโงะ</v>
       </c>
       <c r="C254" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D254" t="str">
         <v>2566</v>
@@ -4725,7 +4725,7 @@
         <v>นางสาวนัสรีน มะสะ</v>
       </c>
       <c r="C255" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D255" t="str">
         <v>2566</v>
@@ -4742,7 +4742,7 @@
         <v>นางสาวนัสรีน หะมิดง</v>
       </c>
       <c r="C256" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D256" t="str">
         <v>2566</v>
@@ -4759,7 +4759,7 @@
         <v>นางสาวนาซีฟะห์ เจะบาการ์</v>
       </c>
       <c r="C257" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D257" t="str">
         <v>2566</v>
@@ -4776,7 +4776,7 @@
         <v>นางสาวนิชดา เขน็ดพืช</v>
       </c>
       <c r="C258" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D258" t="str">
         <v>2566</v>
@@ -4793,7 +4793,7 @@
         <v>นางสาวนิฟารีซาน นิเดร์หะ</v>
       </c>
       <c r="C259" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D259" t="str">
         <v>2566</v>
@@ -4810,7 +4810,7 @@
         <v>นางสาวนิฟารีดา อาลี</v>
       </c>
       <c r="C260" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D260" t="str">
         <v>2566</v>
@@ -4827,7 +4827,7 @@
         <v>นางสาวนิมูนีเราะห์ ลาเตะ</v>
       </c>
       <c r="C261" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D261" t="str">
         <v>2566</v>
@@ -4844,7 +4844,7 @@
         <v>นางสาวนีนา แยแล</v>
       </c>
       <c r="C262" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D262" t="str">
         <v>2566</v>
@@ -4861,7 +4861,7 @@
         <v>นางสาวนีอาม หะยีเลาะ</v>
       </c>
       <c r="C263" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D263" t="str">
         <v>2566</v>
@@ -4878,7 +4878,7 @@
         <v>นางสาวนุรฟาซีลา วะวา</v>
       </c>
       <c r="C264" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D264" t="str">
         <v>2566</v>
@@ -4895,7 +4895,7 @@
         <v>นางสาวนุรมี มะเกะ</v>
       </c>
       <c r="C265" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D265" t="str">
         <v>2566</v>
@@ -4912,7 +4912,7 @@
         <v>นางสาวนูรกัรตีกา อับดุลรอซิด</v>
       </c>
       <c r="C266" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D266" t="str">
         <v>2566</v>
@@ -4929,7 +4929,7 @@
         <v>นางสาวนูรซาฮีดา ติยี</v>
       </c>
       <c r="C267" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D267" t="str">
         <v>2566</v>
@@ -4946,7 +4946,7 @@
         <v>นางสาวนูรตัสนิม สาแล๊ะ</v>
       </c>
       <c r="C268" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D268" t="str">
         <v>2566</v>
@@ -4963,7 +4963,7 @@
         <v>นางสาวนูรไลลา อุมาโมง</v>
       </c>
       <c r="C269" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D269" t="str">
         <v>2566</v>
@@ -4980,7 +4980,7 @@
         <v>นางสาวนูรอัฟนาน เบญดาโอะ</v>
       </c>
       <c r="C270" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D270" t="str">
         <v>2566</v>
@@ -4997,7 +4997,7 @@
         <v>นางสาวนูรฮาซีกีน จิมิ๊</v>
       </c>
       <c r="C271" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D271" t="str">
         <v>2566</v>
@@ -5014,7 +5014,7 @@
         <v>นางสาวนูรฮูดา กาเฮง</v>
       </c>
       <c r="C272" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D272" t="str">
         <v>2566</v>
@@ -5031,7 +5031,7 @@
         <v>นางสาวนูรฮูดา มูดอ</v>
       </c>
       <c r="C273" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D273" t="str">
         <v>2566</v>
@@ -5048,7 +5048,7 @@
         <v>นางสาวนูรีซา อาลี</v>
       </c>
       <c r="C274" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D274" t="str">
         <v>2566</v>
@@ -5065,7 +5065,7 @@
         <v>นางสาวนูรีดา มุคุระ</v>
       </c>
       <c r="C275" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D275" t="str">
         <v>2566</v>
@@ -5082,7 +5082,7 @@
         <v>นางสาวนูรือฟา สามะแอ</v>
       </c>
       <c r="C276" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D276" t="str">
         <v>2566</v>
@@ -5099,7 +5099,7 @@
         <v>นางสาวนูรูอาสมีดา เจ๊ะโซ๊ะ</v>
       </c>
       <c r="C277" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D277" t="str">
         <v>2566</v>
@@ -5116,7 +5116,7 @@
         <v>นางสาวบูหย่า มาเยอะ</v>
       </c>
       <c r="C278" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D278" t="str">
         <v>2566</v>
@@ -5133,7 +5133,7 @@
         <v>นางสาวปัทมา สือนิ</v>
       </c>
       <c r="C279" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D279" t="str">
         <v>2566</v>
@@ -5150,7 +5150,7 @@
         <v>นางสาวปิยวรรณ โสมสุข</v>
       </c>
       <c r="C280" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D280" t="str">
         <v>2566</v>
@@ -5167,7 +5167,7 @@
         <v>นางสาวฟัตเมาะห์ เดมิง</v>
       </c>
       <c r="C281" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D281" t="str">
         <v>2566</v>
@@ -5184,7 +5184,7 @@
         <v>นางสาวฟัรฮานา มะมิง</v>
       </c>
       <c r="C282" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D282" t="str">
         <v>2566</v>
@@ -5201,7 +5201,7 @@
         <v>นางสาวฟาดีละห์ อาบู</v>
       </c>
       <c r="C283" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D283" t="str">
         <v>2566</v>
@@ -5218,7 +5218,7 @@
         <v>นางสาวฟาตอนะห์ หะยีสาแม็ง</v>
       </c>
       <c r="C284" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D284" t="str">
         <v>2566</v>
@@ -5235,7 +5235,7 @@
         <v>นางสาวฟาติน อาแว</v>
       </c>
       <c r="C285" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D285" t="str">
         <v>2566</v>
@@ -5252,7 +5252,7 @@
         <v>นางสาวฟาติมะฮ์ เตาะเมาะ</v>
       </c>
       <c r="C286" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D286" t="str">
         <v>2566</v>
@@ -5269,7 +5269,7 @@
         <v>นางสาวฟาตีฮะห์ โต๊ะกูมามะ</v>
       </c>
       <c r="C287" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D287" t="str">
         <v>2566</v>
@@ -5286,7 +5286,7 @@
         <v>นางสาวฟาตีฮะห์ มะหลง</v>
       </c>
       <c r="C288" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D288" t="str">
         <v>2566</v>
@@ -5303,7 +5303,7 @@
         <v>นางสาวฟิรดาวส์ จาแน</v>
       </c>
       <c r="C289" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D289" t="str">
         <v>2566</v>
@@ -5320,7 +5320,7 @@
         <v>นางสาวมณิกานต์ อาดลูก</v>
       </c>
       <c r="C290" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D290" t="str">
         <v>2566</v>
@@ -5337,7 +5337,7 @@
         <v>นางสาวมาซาอิลณ์ จารู</v>
       </c>
       <c r="C291" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D291" t="str">
         <v>2566</v>
@@ -5354,7 +5354,7 @@
         <v>นางสาวมารีซา ปะดอ</v>
       </c>
       <c r="C292" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D292" t="str">
         <v>2566</v>
@@ -5371,7 +5371,7 @@
         <v>นางสาวมุนซิลีน นะเเหล่</v>
       </c>
       <c r="C293" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D293" t="str">
         <v>2566</v>
@@ -5388,7 +5388,7 @@
         <v>นางสาวมุมตัซร์ สามอ</v>
       </c>
       <c r="C294" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D294" t="str">
         <v>2566</v>
@@ -5405,7 +5405,7 @@
         <v>นางสาวมุมีนะห์ วาแฮ</v>
       </c>
       <c r="C295" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D295" t="str">
         <v>2566</v>
@@ -5422,7 +5422,7 @@
         <v>นางสาวนัสริน กาเกาะ</v>
       </c>
       <c r="C296" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D296" t="str">
         <v>2566</v>
@@ -5439,7 +5439,7 @@
         <v>นางสาววันอัสมาร์ท สามะอาลี</v>
       </c>
       <c r="C297" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D297" t="str">
         <v>2566</v>
@@ -5456,7 +5456,7 @@
         <v>นางสาววารุณีย์ ดาโอ๊ะ</v>
       </c>
       <c r="C298" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D298" t="str">
         <v>2566</v>
@@ -5473,7 +5473,7 @@
         <v>นางสาวสายสุดา สือรี</v>
       </c>
       <c r="C299" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D299" t="str">
         <v>2566</v>
@@ -5490,7 +5490,7 @@
         <v>นางสาวสุกันยา อามอ</v>
       </c>
       <c r="C300" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D300" t="str">
         <v>2566</v>
@@ -5507,7 +5507,7 @@
         <v>นางสาวสุรินี ยะผา</v>
       </c>
       <c r="C301" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D301" t="str">
         <v>2566</v>
@@ -5524,7 +5524,7 @@
         <v>นางสาวอธิตา สุวรรณชาตรี</v>
       </c>
       <c r="C302" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D302" t="str">
         <v>2566</v>
@@ -5541,7 +5541,7 @@
         <v>นางสาวอธิยยะฮ์ สะอะ</v>
       </c>
       <c r="C303" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D303" t="str">
         <v>2566</v>
@@ -5558,7 +5558,7 @@
         <v>นางสาวอัมนีย์ นือเร็ง</v>
       </c>
       <c r="C304" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D304" t="str">
         <v>2566</v>
@@ -5575,7 +5575,7 @@
         <v>นางสาวอัยมี คาเดร์</v>
       </c>
       <c r="C305" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D305" t="str">
         <v>2566</v>
@@ -5592,7 +5592,7 @@
         <v>นางสาวอาซีซะห์ มะดิเยาะ</v>
       </c>
       <c r="C306" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D306" t="str">
         <v>2566</v>
@@ -5609,7 +5609,7 @@
         <v>นางสาวอาซูรา เมาะดีเยาะ</v>
       </c>
       <c r="C307" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D307" t="str">
         <v>2566</v>
@@ -5626,7 +5626,7 @@
         <v>นางสาวอามานี บือโต</v>
       </c>
       <c r="C308" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D308" t="str">
         <v>2566</v>
@@ -5643,7 +5643,7 @@
         <v>นางสาวอาวาตีฟ เจะซู</v>
       </c>
       <c r="C309" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D309" t="str">
         <v>2566</v>
@@ -5660,7 +5660,7 @@
         <v>นางสาวอาอีซะห์ หะยีมะลี</v>
       </c>
       <c r="C310" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D310" t="str">
         <v>2566</v>
@@ -5677,7 +5677,7 @@
         <v>นางสาวอิบตีซาม อะยูยา</v>
       </c>
       <c r="C311" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D311" t="str">
         <v>2566</v>
@@ -5694,7 +5694,7 @@
         <v>นางสาวอิฟฟะฮ์ หะยีสือแม</v>
       </c>
       <c r="C312" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D312" t="str">
         <v>2566</v>
@@ -5711,7 +5711,7 @@
         <v>นางสาวอีนัส อายีมะสาและ</v>
       </c>
       <c r="C313" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D313" t="str">
         <v>2566</v>
@@ -5728,7 +5728,7 @@
         <v>นางสาวอุสวะห์ วาโด</v>
       </c>
       <c r="C314" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D314" t="str">
         <v>2566</v>
@@ -5745,7 +5745,7 @@
         <v>นางสาวฮันนาน เซ็ง</v>
       </c>
       <c r="C315" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D315" t="str">
         <v>2566</v>
@@ -5762,7 +5762,7 @@
         <v>นางสาวฮัยฟา หะยีเตะ</v>
       </c>
       <c r="C316" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D316" t="str">
         <v>2566</v>
@@ -5779,7 +5779,7 @@
         <v>นางสาวฮัสวาน่า เกตุแก้ว</v>
       </c>
       <c r="C317" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D317" t="str">
         <v>2566</v>
@@ -5796,7 +5796,7 @@
         <v>นางสาวฮานีฟา กาลูแป</v>
       </c>
       <c r="C318" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D318" t="str">
         <v>2566</v>
@@ -5813,7 +5813,7 @@
         <v>นางสาวฮุสนา เจ๊ะลัง</v>
       </c>
       <c r="C319" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D319" t="str">
         <v>2566</v>
@@ -5830,7 +5830,7 @@
         <v>นางสาวซัยดาณี มะอิลา</v>
       </c>
       <c r="C320" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D320" t="str">
         <v>2566</v>
@@ -5847,7 +5847,7 @@
         <v>นางสาวอามีรา ปะตะมอ</v>
       </c>
       <c r="C321" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D321" t="str">
         <v>2566</v>
@@ -5864,7 +5864,7 @@
         <v>นางสาวอิบตีซาน แดวอสนุง</v>
       </c>
       <c r="C322" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D322" t="str">
         <v>2566</v>
@@ -5881,7 +5881,7 @@
         <v>นางสาวซุลฟา เจ๊ะแฮ</v>
       </c>
       <c r="C323" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D323" t="str">
         <v>2566</v>
@@ -5898,7 +5898,7 @@
         <v>นางสาววันนาเดียร์ เถาะ</v>
       </c>
       <c r="C324" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D324" t="str">
         <v>2566</v>
@@ -5915,7 +5915,7 @@
         <v>นางสาวสิรินดา สุระกำแหง</v>
       </c>
       <c r="C325" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D325" t="str">
         <v>2566</v>
@@ -5932,7 +5932,7 @@
         <v>นางสาววีดาร์ด หนูพริ้ม</v>
       </c>
       <c r="C326" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D326" t="str">
         <v>2566</v>
@@ -5949,7 +5949,7 @@
         <v>นางสาวอาดีลา เปาะแต</v>
       </c>
       <c r="C327" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D327" t="str">
         <v>2566</v>
@@ -5966,7 +5966,7 @@
         <v>นางสาวอัฟนัน บือราเฮง</v>
       </c>
       <c r="C328" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D328" t="str">
         <v>2566</v>
@@ -5983,7 +5983,7 @@
         <v>นายวันซาฟิอี ดอแม</v>
       </c>
       <c r="C329" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>เคมี</v>
       </c>
       <c r="D329" t="str">
         <v>2566</v>
@@ -6000,7 +6000,7 @@
         <v>นางสาวนูรนายีฮะห์ บือราเฮง</v>
       </c>
       <c r="C330" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>เคมี</v>
       </c>
       <c r="D330" t="str">
         <v>2566</v>
@@ -6017,7 +6017,7 @@
         <v>นายซุลกีฟลี โตะเดร์</v>
       </c>
       <c r="C331" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D331" t="str">
         <v>2566</v>
@@ -6034,7 +6034,7 @@
         <v>นายฟาริด แนปิแน</v>
       </c>
       <c r="C332" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D332" t="str">
         <v>2566</v>
@@ -6051,7 +6051,7 @@
         <v>นายมุซรีฟ เลาะตะโละ</v>
       </c>
       <c r="C333" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D333" t="str">
         <v>2566</v>
@@ -6068,7 +6068,7 @@
         <v>นายมูหำหมัดนะห์ดี โสล่า</v>
       </c>
       <c r="C334" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D334" t="str">
         <v>2566</v>
@@ -6085,7 +6085,7 @@
         <v>นายรุ่งโรจน์ สีสดใส</v>
       </c>
       <c r="C335" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D335" t="str">
         <v>2566</v>
@@ -6102,7 +6102,7 @@
         <v>นายอะฟานดี มูเซะ</v>
       </c>
       <c r="C336" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D336" t="str">
         <v>2566</v>
@@ -6119,7 +6119,7 @@
         <v>นายอานีส มะลิสด</v>
       </c>
       <c r="C337" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D337" t="str">
         <v>2566</v>
@@ -6136,7 +6136,7 @@
         <v>นางสาวซัลวะห์ ยูโซะ</v>
       </c>
       <c r="C338" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D338" t="str">
         <v>2566</v>
@@ -6153,7 +6153,7 @@
         <v>นางสาวซูลฟา ตาเยะ</v>
       </c>
       <c r="C339" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D339" t="str">
         <v>2566</v>
@@ -6170,7 +6170,7 @@
         <v>นางสาวซูลวานี บาราเฮง</v>
       </c>
       <c r="C340" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D340" t="str">
         <v>2566</v>
@@ -6187,7 +6187,7 @@
         <v>นางสาวดวงใจ ยิ้มยวน</v>
       </c>
       <c r="C341" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D341" t="str">
         <v>2566</v>
@@ -6204,7 +6204,7 @@
         <v>นางสาวนูดียา ดัมแหล๊ะ</v>
       </c>
       <c r="C342" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D342" t="str">
         <v>2566</v>
@@ -6221,7 +6221,7 @@
         <v>นางสาวนูฮา ยูโซ๊ะ</v>
       </c>
       <c r="C343" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D343" t="str">
         <v>2566</v>
@@ -6238,7 +6238,7 @@
         <v>นางสาวบุศรินทร์ มะสำอินทร์</v>
       </c>
       <c r="C344" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D344" t="str">
         <v>2566</v>
@@ -6255,7 +6255,7 @@
         <v>นางสาวฟิรดาวซ์ เสะและ</v>
       </c>
       <c r="C345" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D345" t="str">
         <v>2566</v>
@@ -6272,7 +6272,7 @@
         <v>นางสาวสุจินดา สาอะ</v>
       </c>
       <c r="C346" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D346" t="str">
         <v>2566</v>
@@ -6289,7 +6289,7 @@
         <v>นางสาวอัฟนัน สาและ</v>
       </c>
       <c r="C347" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D347" t="str">
         <v>2566</v>
@@ -6306,7 +6306,7 @@
         <v>นางสาวฮัซมี ประเสริฐ</v>
       </c>
       <c r="C348" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D348" t="str">
         <v>2566</v>
@@ -6323,7 +6323,7 @@
         <v>นางสาวฮิลมีย์ เอ็มเล่ง</v>
       </c>
       <c r="C349" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D349" t="str">
         <v>2566</v>
@@ -6340,7 +6340,7 @@
         <v>นางสาวมนัสนันท์ ยูซบ</v>
       </c>
       <c r="C350" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D350" t="str">
         <v>2566</v>
@@ -6357,7 +6357,7 @@
         <v>นางสาวสำนักทะเบียน สทว</v>
       </c>
       <c r="C351" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D351" t="str">
         <v>2566</v>
@@ -6374,7 +6374,7 @@
         <v>นายฮาริส หลีเยาว์</v>
       </c>
       <c r="C352" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D352" t="str">
         <v>2566</v>
@@ -6391,7 +6391,7 @@
         <v>นายนอีฟ ประเสริฐดำ</v>
       </c>
       <c r="C353" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D353" t="str">
         <v>2566</v>
@@ -6408,7 +6408,7 @@
         <v>นายฟิรดาวน์ ยูโซ๊ะ</v>
       </c>
       <c r="C354" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D354" t="str">
         <v>2566</v>
@@ -6425,7 +6425,7 @@
         <v>นายฟุรกอน หลำหม๊ะ</v>
       </c>
       <c r="C355" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D355" t="str">
         <v>2566</v>
@@ -6442,7 +6442,7 @@
         <v>นายมูฮำหมัดอามีรุล อาแย</v>
       </c>
       <c r="C356" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D356" t="str">
         <v>2566</v>
@@ -6459,7 +6459,7 @@
         <v>นายอนัส อุปมา</v>
       </c>
       <c r="C357" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D357" t="str">
         <v>2566</v>
@@ -6476,7 +6476,7 @@
         <v>นายซอบัร มุ่งหมั่นทำ</v>
       </c>
       <c r="C358" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D358" t="str">
         <v>2566</v>
@@ -6493,7 +6493,7 @@
         <v>นายอับดุล ถนอมรัก</v>
       </c>
       <c r="C359" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D359" t="str">
         <v>2566</v>
@@ -6510,7 +6510,7 @@
         <v>นางสาวบูสหร่อ หะยีมามะ</v>
       </c>
       <c r="C360" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D360" t="str">
         <v>2566</v>
@@ -6527,7 +6527,7 @@
         <v>นางสาวมนัสนันท์ ยูซบ</v>
       </c>
       <c r="C361" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D361" t="str">
         <v>2566</v>
@@ -6544,7 +6544,7 @@
         <v>นางสาวมุมีนะห์ มาหิเละ</v>
       </c>
       <c r="C362" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D362" t="str">
         <v>2566</v>
@@ -6561,7 +6561,7 @@
         <v>นางสาวอัฟนาน ดอเลาะ</v>
       </c>
       <c r="C363" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D363" t="str">
         <v>2566</v>
@@ -6578,7 +6578,7 @@
         <v>นางสาวอัยนาอ์ อาดมะเร๊ะ</v>
       </c>
       <c r="C364" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D364" t="str">
         <v>2566</v>
@@ -6595,7 +6595,7 @@
         <v>นายซอและฮ์ สาแม็ง</v>
       </c>
       <c r="C365" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D365" t="str">
         <v>2566</v>
@@ -6612,7 +6612,7 @@
         <v>นายซูอารฟาน ดือเระ</v>
       </c>
       <c r="C366" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D366" t="str">
         <v>2566</v>
@@ -6629,7 +6629,7 @@
         <v>นายมุคลิส เจ๊ะเเน</v>
       </c>
       <c r="C367" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D367" t="str">
         <v>2566</v>
@@ -6646,7 +6646,7 @@
         <v>นายมุมิน รออิตี</v>
       </c>
       <c r="C368" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D368" t="str">
         <v>2566</v>
@@ -6663,7 +6663,7 @@
         <v>นายยูไนดี มาชัย</v>
       </c>
       <c r="C369" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D369" t="str">
         <v>2566</v>
@@ -6680,7 +6680,7 @@
         <v>นายอับดุลฮาฟิส แวนะไล</v>
       </c>
       <c r="C370" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D370" t="str">
         <v>2566</v>
@@ -6697,7 +6697,7 @@
         <v>นายมูหำหมัดนะห์ดี โสล่า</v>
       </c>
       <c r="C371" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D371" t="str">
         <v>2566</v>
@@ -6714,7 +6714,7 @@
         <v>นางสาว</v>
       </c>
       <c r="C372" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D372" t="str">
         <v>2566</v>
@@ -6731,7 +6731,7 @@
         <v>นางสาวนัจมี เเตนิมะ</v>
       </c>
       <c r="C373" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D373" t="str">
         <v>2566</v>
@@ -6748,7 +6748,7 @@
         <v>นางสาวนัสรีย์ โต๊ะเเหล้</v>
       </c>
       <c r="C374" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D374" t="str">
         <v>2566</v>
@@ -6765,7 +6765,7 @@
         <v>นางสาวนูรฟาติน อีซอ</v>
       </c>
       <c r="C375" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D375" t="str">
         <v>2566</v>
@@ -6782,7 +6782,7 @@
         <v>นางสาวฟิรดาวส์ ยะผา</v>
       </c>
       <c r="C376" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D376" t="str">
         <v>2566</v>
@@ -6799,7 +6799,7 @@
         <v>นางสาวมุมีนะห์ ดอเลาะ</v>
       </c>
       <c r="C377" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D377" t="str">
         <v>2566</v>
@@ -6816,7 +6816,7 @@
         <v>นางสาวรุวัยดา เริงสมุทร</v>
       </c>
       <c r="C378" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D378" t="str">
         <v>2566</v>
@@ -6833,7 +6833,7 @@
         <v>นางสาววันณา อาแว</v>
       </c>
       <c r="C379" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D379" t="str">
         <v>2566</v>
@@ -6850,7 +6850,7 @@
         <v>นางสาววันนาเดียร์ เถาะ</v>
       </c>
       <c r="C380" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D380" t="str">
         <v>2566</v>
@@ -6867,7 +6867,7 @@
         <v>นางสาวอลาอ์ มะดอเลาะ</v>
       </c>
       <c r="C381" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D381" t="str">
         <v>2566</v>
@@ -6884,7 +6884,7 @@
         <v>นางสาวอัสมะ หะยีนาแว</v>
       </c>
       <c r="C382" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D382" t="str">
         <v>2566</v>
@@ -6901,7 +6901,7 @@
         <v>นางสาวอัสมาอ กือโด</v>
       </c>
       <c r="C383" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D383" t="str">
         <v>2566</v>
@@ -6918,7 +6918,7 @@
         <v>นางสาวอาดีลา เปาะแต</v>
       </c>
       <c r="C384" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D384" t="str">
         <v>2566</v>
@@ -6935,7 +6935,7 @@
         <v>นางสาวอาริณีย์ แม</v>
       </c>
       <c r="C385" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D385" t="str">
         <v>2566</v>
@@ -6952,7 +6952,7 @@
         <v>นางสาวอิลฮาม ประสารการ</v>
       </c>
       <c r="C386" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D386" t="str">
         <v>2566</v>
@@ -6969,7 +6969,7 @@
         <v>นางสาวฟาตีมะฮ์ เกาะแจ</v>
       </c>
       <c r="C387" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D387" t="str">
         <v>2566</v>
@@ -6986,7 +6986,7 @@
         <v>นางสาวตัสนีม แดเบาะ</v>
       </c>
       <c r="C388" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D388" t="str">
         <v>2566</v>
@@ -7003,7 +7003,7 @@
         <v>นางสาวอัฟนัน บือราเฮง</v>
       </c>
       <c r="C389" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D389" t="str">
         <v>2566</v>
@@ -7020,7 +7020,7 @@
         <v>นางสาวฟิรเดาส์ บุญแต่ง</v>
       </c>
       <c r="C390" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D390" t="str">
         <v>2566</v>
@@ -7037,7 +7037,7 @@
         <v>นางสาวซอลีฮะห์ ดอเลาะ</v>
       </c>
       <c r="C391" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D391" t="str">
         <v>2566</v>
@@ -7054,7 +7054,7 @@
         <v>นางสาวกรีมะห์ ลาเต๊ะ</v>
       </c>
       <c r="C392" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D392" t="str">
         <v>2566</v>
@@ -7071,7 +7071,7 @@
         <v>นางสาวซูรีนา ยูโซะ</v>
       </c>
       <c r="C393" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D393" t="str">
         <v>2566</v>
@@ -7088,7 +7088,7 @@
         <v>นายซอลาฮุดดีน บูละ</v>
       </c>
       <c r="C394" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D394" t="str">
         <v>2566</v>
@@ -7105,7 +7105,7 @@
         <v>นายซัลมาน รอดเข็ม</v>
       </c>
       <c r="C395" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D395" t="str">
         <v>2566</v>
@@ -7122,7 +7122,7 @@
         <v>นายซุบฮาน ยะเอะ</v>
       </c>
       <c r="C396" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D396" t="str">
         <v>2566</v>
@@ -7139,7 +7139,7 @@
         <v>นายซุลกะมาล แมทาลง</v>
       </c>
       <c r="C397" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D397" t="str">
         <v>2566</v>
@@ -7156,7 +7156,7 @@
         <v>นายต่วนชามีม มือกะหามะ</v>
       </c>
       <c r="C398" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D398" t="str">
         <v>2566</v>
@@ -7173,7 +7173,7 @@
         <v>นายมูฮำหมัดตัจรีย์ สะตีมือมะ</v>
       </c>
       <c r="C399" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D399" t="str">
         <v>2566</v>
@@ -7190,7 +7190,7 @@
         <v>นายนิโค ออสมานี</v>
       </c>
       <c r="C400" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D400" t="str">
         <v>2566</v>
@@ -7207,7 +7207,7 @@
         <v>นายนูรุดดีน แขวงบู</v>
       </c>
       <c r="C401" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D401" t="str">
         <v>2566</v>
@@ -7224,7 +7224,7 @@
         <v>นายมูฮัมหมัดไซฟู สะมาโระ</v>
       </c>
       <c r="C402" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D402" t="str">
         <v>2566</v>
@@ -7241,7 +7241,7 @@
         <v>นายสุลตอล มูฮำหมัดอาฟาฟ</v>
       </c>
       <c r="C403" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D403" t="str">
         <v>2566</v>
@@ -7258,7 +7258,7 @@
         <v>นายอะฟีฟ เส็นโสม</v>
       </c>
       <c r="C404" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D404" t="str">
         <v>2566</v>
@@ -7275,7 +7275,7 @@
         <v>นายอะหมัดฮาบีบี เหล็บบิลหล๊ะ</v>
       </c>
       <c r="C405" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D405" t="str">
         <v>2566</v>
@@ -7292,7 +7292,7 @@
         <v>นายอาแซ สะมะแอลีมา</v>
       </c>
       <c r="C406" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D406" t="str">
         <v>2566</v>
@@ -7309,7 +7309,7 @@
         <v>นายอารัช แดงประดับ</v>
       </c>
       <c r="C407" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D407" t="str">
         <v>2566</v>
@@ -7326,7 +7326,7 @@
         <v>นายอิรฟาน โต๊ะลง</v>
       </c>
       <c r="C408" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D408" t="str">
         <v>2566</v>
@@ -7343,7 +7343,7 @@
         <v>นายฮานีฟ อาลีลูกา</v>
       </c>
       <c r="C409" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D409" t="str">
         <v>2566</v>
@@ -7360,7 +7360,7 @@
         <v>นายจักกฤษ นุ้ยสัน</v>
       </c>
       <c r="C410" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D410" t="str">
         <v>2566</v>
@@ -7377,7 +7377,7 @@
         <v>นางสาวกอมารียะห์ ยาโงะ</v>
       </c>
       <c r="C411" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D411" t="str">
         <v>2566</v>
@@ -7394,7 +7394,7 @@
         <v>นางสาวเกาซัร กูมีรอ</v>
       </c>
       <c r="C412" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D412" t="str">
         <v>2566</v>
@@ -7411,7 +7411,7 @@
         <v>นางสาวคอรียา เตียงงา</v>
       </c>
       <c r="C413" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D413" t="str">
         <v>2566</v>
@@ -7428,7 +7428,7 @@
         <v>นางสาวซอฟียะห์ อีแตเบ็ง</v>
       </c>
       <c r="C414" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D414" t="str">
         <v>2566</v>
@@ -7445,7 +7445,7 @@
         <v>นางสาวซัลวา เละโซ๊ะ</v>
       </c>
       <c r="C415" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D415" t="str">
         <v>2566</v>
@@ -7462,7 +7462,7 @@
         <v>นางสาวซินนี่ โอรามหลง</v>
       </c>
       <c r="C416" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D416" t="str">
         <v>2566</v>
@@ -7479,7 +7479,7 @@
         <v>นางสาวซีตีซาร่า นิเดร์</v>
       </c>
       <c r="C417" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D417" t="str">
         <v>2566</v>
@@ -7496,7 +7496,7 @@
         <v>นางสาวซุลฟา ลาเต๊ะเลาะ</v>
       </c>
       <c r="C418" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D418" t="str">
         <v>2566</v>
@@ -7513,7 +7513,7 @@
         <v>นางสาวซูซัน ปะแตบือแน</v>
       </c>
       <c r="C419" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D419" t="str">
         <v>2566</v>
@@ -7530,7 +7530,7 @@
         <v>นางสาวซูฮาดา มะลาเฮง</v>
       </c>
       <c r="C420" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D420" t="str">
         <v>2566</v>
@@ -7547,7 +7547,7 @@
         <v>นางสาวไซเฆ๊าะฮ์ หะยีแวนิ</v>
       </c>
       <c r="C421" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D421" t="str">
         <v>2566</v>
@@ -7564,7 +7564,7 @@
         <v>นางสาวญัซมิน เจ๊ะสารี</v>
       </c>
       <c r="C422" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D422" t="str">
         <v>2566</v>
@@ -7581,7 +7581,7 @@
         <v>นางสาวญามีล๊ะห์ ปายังซายี</v>
       </c>
       <c r="C423" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D423" t="str">
         <v>2566</v>
@@ -7598,7 +7598,7 @@
         <v>นางสาวณัดญวา ไชยภักดี</v>
       </c>
       <c r="C424" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D424" t="str">
         <v>2566</v>
@@ -7615,7 +7615,7 @@
         <v>นางสาวตัสนีม อับดุลสตา</v>
       </c>
       <c r="C425" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D425" t="str">
         <v>2566</v>
@@ -7632,7 +7632,7 @@
         <v>นางสาวตาฮานี สาเล็ง</v>
       </c>
       <c r="C426" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D426" t="str">
         <v>2566</v>
@@ -7649,7 +7649,7 @@
         <v>นางสาวนริศา ปิ่นตุหรัด</v>
       </c>
       <c r="C427" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D427" t="str">
         <v>2566</v>
@@ -7666,7 +7666,7 @@
         <v>นางสาวนัจมีย์ ดือราโอะ</v>
       </c>
       <c r="C428" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D428" t="str">
         <v>2566</v>
@@ -7683,7 +7683,7 @@
         <v>นางสาวนาดียา หวันเก</v>
       </c>
       <c r="C429" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D429" t="str">
         <v>2566</v>
@@ -7700,7 +7700,7 @@
         <v>นางสาวนิมัสฮูดา นิเดร์หะ</v>
       </c>
       <c r="C430" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D430" t="str">
         <v>2566</v>
@@ -7717,7 +7717,7 @@
         <v>นางสาวนิสา บิลอะหมัด</v>
       </c>
       <c r="C431" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D431" t="str">
         <v>2566</v>
@@ -7734,7 +7734,7 @@
         <v>นางสาวนูรดานีน แก้วเกิด</v>
       </c>
       <c r="C432" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D432" t="str">
         <v>2566</v>
@@ -7751,7 +7751,7 @@
         <v>นางสาวนูรไลลา เต๊ะปูยู</v>
       </c>
       <c r="C433" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D433" t="str">
         <v>2566</v>
@@ -7768,7 +7768,7 @@
         <v>นางสาวตูแวฮาซียะห์ โลบือราเฮง</v>
       </c>
       <c r="C434" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D434" t="str">
         <v>2566</v>
@@ -7785,7 +7785,7 @@
         <v>นางสาวนูรอีมานี มาหะมะ</v>
       </c>
       <c r="C435" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D435" t="str">
         <v>2566</v>
@@ -7802,7 +7802,7 @@
         <v>นางสาวนูรฮาซีลา เจะเลาะ</v>
       </c>
       <c r="C436" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D436" t="str">
         <v>2566</v>
@@ -7819,7 +7819,7 @@
         <v>นางสาวนูรีมัน บากะ</v>
       </c>
       <c r="C437" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D437" t="str">
         <v>2566</v>
@@ -7836,7 +7836,7 @@
         <v>นางสาวนูรียะห์ สาและ</v>
       </c>
       <c r="C438" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D438" t="str">
         <v>2566</v>
@@ -7853,7 +7853,7 @@
         <v>นางสาวเนาวาร์ มะดีเยาะ</v>
       </c>
       <c r="C439" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D439" t="str">
         <v>2566</v>
@@ -7870,7 +7870,7 @@
         <v>นางสาวบัลกิส อายา</v>
       </c>
       <c r="C440" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D440" t="str">
         <v>2566</v>
@@ -7887,7 +7887,7 @@
         <v>นางสาวบัลกีส ยามา</v>
       </c>
       <c r="C441" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D441" t="str">
         <v>2566</v>
@@ -7904,7 +7904,7 @@
         <v>นางสาวฟาฏิน กาเดร์</v>
       </c>
       <c r="C442" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D442" t="str">
         <v>2566</v>
@@ -7921,7 +7921,7 @@
         <v>นางสาวฟาดีลา มามะ</v>
       </c>
       <c r="C443" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D443" t="str">
         <v>2566</v>
@@ -7938,7 +7938,7 @@
         <v>นางสาวฟาริชตา ดือรานิง</v>
       </c>
       <c r="C444" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D444" t="str">
         <v>2566</v>
@@ -7955,7 +7955,7 @@
         <v>นางสาวฟารีดา แนมน้อย</v>
       </c>
       <c r="C445" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D445" t="str">
         <v>2566</v>
@@ -7972,7 +7972,7 @@
         <v>นางสาวฟารีดา มุไท</v>
       </c>
       <c r="C446" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D446" t="str">
         <v>2566</v>
@@ -7989,7 +7989,7 @@
         <v>นางสาวฟิตยะห์ วาด๊ะ</v>
       </c>
       <c r="C447" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D447" t="str">
         <v>2566</v>
@@ -8006,7 +8006,7 @@
         <v>นางสาวฟิรดาวส์ หะยีตาเฮ</v>
       </c>
       <c r="C448" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D448" t="str">
         <v>2566</v>
@@ -8023,7 +8023,7 @@
         <v>นางสาวมัรฮามา จิเหม</v>
       </c>
       <c r="C449" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D449" t="str">
         <v>2566</v>
@@ -8040,7 +8040,7 @@
         <v>นางสาววันฟารีดา กูเเม</v>
       </c>
       <c r="C450" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D450" t="str">
         <v>2566</v>
@@ -8057,7 +8057,7 @@
         <v>นางสาวอะศีละฮ์ โน๊ะ</v>
       </c>
       <c r="C451" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D451" t="str">
         <v>2566</v>
@@ -8074,7 +8074,7 @@
         <v>นางสาวอารีนี ลาเต๊ะ</v>
       </c>
       <c r="C452" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D452" t="str">
         <v>2566</v>
@@ -8091,7 +8091,7 @@
         <v>นางสาวตัสนีม อูมา</v>
       </c>
       <c r="C453" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D453" t="str">
         <v>2566</v>
@@ -8108,7 +8108,7 @@
         <v>นางสาวนิฮันนาน เจ๊ะเล็ม</v>
       </c>
       <c r="C454" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D454" t="str">
         <v>2566</v>
@@ -8125,7 +8125,7 @@
         <v>นางสาวฟาดีละห์ อิสัน</v>
       </c>
       <c r="C455" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D455" t="str">
         <v>2566</v>
@@ -8142,7 +8142,7 @@
         <v>นางสาวรัยญาน มะวิง</v>
       </c>
       <c r="C456" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D456" t="str">
         <v>2566</v>
@@ -8159,7 +8159,7 @@
         <v>นางสาวรีฮาม เมฆลอย</v>
       </c>
       <c r="C457" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D457" t="str">
         <v>2566</v>
@@ -8176,7 +8176,7 @@
         <v>นางสาวรุ่งรัศมี จิตต์หมวด</v>
       </c>
       <c r="C458" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D458" t="str">
         <v>2566</v>
@@ -8193,7 +8193,7 @@
         <v>นางสาววรัชยา อาหมัด</v>
       </c>
       <c r="C459" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D459" t="str">
         <v>2566</v>
@@ -8210,7 +8210,7 @@
         <v>นางสาววัญดา คาเด</v>
       </c>
       <c r="C460" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D460" t="str">
         <v>2566</v>
@@ -8227,7 +8227,7 @@
         <v>นางสาววายุรินทร์ เริงสมุทร</v>
       </c>
       <c r="C461" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D461" t="str">
         <v>2566</v>
@@ -8244,7 +8244,7 @@
         <v>นางสาววิลาสินี ลูกเจะ</v>
       </c>
       <c r="C462" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D462" t="str">
         <v>2566</v>
@@ -8261,7 +8261,7 @@
         <v>นางสาววีดาร์ด หนูพริ้ม</v>
       </c>
       <c r="C463" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D463" t="str">
         <v>2566</v>
@@ -8278,7 +8278,7 @@
         <v>นางสาววีรยา ศิริยามัน</v>
       </c>
       <c r="C464" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D464" t="str">
         <v>2566</v>
@@ -8295,7 +8295,7 @@
         <v>นางสาวศอลิหะฮ์ มาหะ</v>
       </c>
       <c r="C465" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D465" t="str">
         <v>2566</v>
@@ -8312,7 +8312,7 @@
         <v>นางสาวสาวิตรี ดอเล๊าะ</v>
       </c>
       <c r="C466" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D466" t="str">
         <v>2566</v>
@@ -8329,7 +8329,7 @@
         <v>นางสาวสีตีนุรซาฟีกา บินหะยียะโกบ</v>
       </c>
       <c r="C467" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D467" t="str">
         <v>2566</v>
@@ -8346,7 +8346,7 @@
         <v>นางสาวสูไฮนี ยือลาแป</v>
       </c>
       <c r="C468" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D468" t="str">
         <v>2566</v>
@@ -8363,7 +8363,7 @@
         <v>นางสาวอลิชา มะลิวัล</v>
       </c>
       <c r="C469" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D469" t="str">
         <v>2566</v>
@@ -8380,7 +8380,7 @@
         <v>นางสาวอัยมี่ย์ โตะบาโก</v>
       </c>
       <c r="C470" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D470" t="str">
         <v>2566</v>
@@ -8397,7 +8397,7 @@
         <v>นางสาวอัลอามาลีนา กียะ</v>
       </c>
       <c r="C471" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D471" t="str">
         <v>2566</v>
@@ -8414,7 +8414,7 @@
         <v>นางสาวอาซียะห์ อุเซ็น</v>
       </c>
       <c r="C472" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D472" t="str">
         <v>2566</v>
@@ -8431,7 +8431,7 @@
         <v>นางสาวอาตีระห์ มะสูเป็ง</v>
       </c>
       <c r="C473" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D473" t="str">
         <v>2566</v>
@@ -8448,7 +8448,7 @@
         <v>นางสาวอามูนา ซีดิ</v>
       </c>
       <c r="C474" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D474" t="str">
         <v>2566</v>
@@ -8465,7 +8465,7 @@
         <v>นางสาวอิลฮัม วาแล๊ะ</v>
       </c>
       <c r="C475" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D475" t="str">
         <v>2566</v>
@@ -8482,7 +8482,7 @@
         <v>นางสาวอิลฮามีย์ หมาดบากา</v>
       </c>
       <c r="C476" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D476" t="str">
         <v>2566</v>
@@ -8499,7 +8499,7 @@
         <v>นางสาวอิสเราะอ์ มือเลาะหะแม</v>
       </c>
       <c r="C477" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D477" t="str">
         <v>2566</v>
@@ -8516,7 +8516,7 @@
         <v>นางสาวเอาว์ฟา สาและ</v>
       </c>
       <c r="C478" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D478" t="str">
         <v>2566</v>
@@ -8533,7 +8533,7 @@
         <v>นางสาวฮาบิบตี อาลี</v>
       </c>
       <c r="C479" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D479" t="str">
         <v>2566</v>
@@ -8550,7 +8550,7 @@
         <v>นางสาวอิฟตีซาม อาแว</v>
       </c>
       <c r="C480" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D480" t="str">
         <v>2566</v>
@@ -8567,7 +8567,7 @@
         <v>นางสาวตัสนีม มะดีเยาะ</v>
       </c>
       <c r="C481" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D481" t="str">
         <v>2566</v>
@@ -8584,7 +8584,7 @@
         <v>นางสาวนัสริล สาและ</v>
       </c>
       <c r="C482" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D482" t="str">
         <v>2566</v>
@@ -8601,7 +8601,7 @@
         <v>นางสาวอาฟฟะห์ เจะเลาะ</v>
       </c>
       <c r="C483" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D483" t="str">
         <v>2566</v>
@@ -8618,7 +8618,7 @@
         <v>นายซาคิริน อุมา</v>
       </c>
       <c r="C484" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D484" t="str">
         <v>2566</v>
@@ -8635,7 +8635,7 @@
         <v>นายซิลมี เจะเลง</v>
       </c>
       <c r="C485" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D485" t="str">
         <v>2566</v>
@@ -8652,7 +8652,7 @@
         <v>นายซูไฮมี แวหะยี</v>
       </c>
       <c r="C486" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D486" t="str">
         <v>2566</v>
@@ -8669,7 +8669,7 @@
         <v>นายมุสลิม จารง</v>
       </c>
       <c r="C487" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D487" t="str">
         <v>2566</v>
@@ -8686,7 +8686,7 @@
         <v>นายมูหามะนัสรู นิแด</v>
       </c>
       <c r="C488" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D488" t="str">
         <v>2566</v>
@@ -8703,7 +8703,7 @@
         <v>นายกูมุคลิซ ตวันดอเลาะ</v>
       </c>
       <c r="C489" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D489" t="str">
         <v>2567</v>
@@ -8720,7 +8720,7 @@
         <v>นายชารีฟ บิลนุภัทร</v>
       </c>
       <c r="C490" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D490" t="str">
         <v>2567</v>
@@ -8737,7 +8737,7 @@
         <v>นายธฤต รอดหมาน</v>
       </c>
       <c r="C491" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D491" t="str">
         <v>2567</v>
@@ -8754,7 +8754,7 @@
         <v>นายบาบัร เจริญจิตต์</v>
       </c>
       <c r="C492" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D492" t="str">
         <v>2567</v>
@@ -8771,7 +8771,7 @@
         <v>นายฟัฮมี มะสารี</v>
       </c>
       <c r="C493" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D493" t="str">
         <v>2567</v>
@@ -8788,7 +8788,7 @@
         <v>นายเฟาวาซ โต๊ะมะ</v>
       </c>
       <c r="C494" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D494" t="str">
         <v>2567</v>
@@ -8805,7 +8805,7 @@
         <v>นายมุสกาน มูฮำหมัดอารี</v>
       </c>
       <c r="C495" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D495" t="str">
         <v>2567</v>
@@ -8822,7 +8822,7 @@
         <v>นายมูซอฟัต เบ็ญละโต๊ะ</v>
       </c>
       <c r="C496" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D496" t="str">
         <v>2567</v>
@@ -8839,7 +8839,7 @@
         <v>นายมูซากีฟ สือแม</v>
       </c>
       <c r="C497" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D497" t="str">
         <v>2567</v>
@@ -8856,7 +8856,7 @@
         <v>นายมูนีร อับดุลเล๊าะ</v>
       </c>
       <c r="C498" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D498" t="str">
         <v>2567</v>
@@ -8873,7 +8873,7 @@
         <v>นายมูฮัมมัดอิรฮัม ดอฆอ</v>
       </c>
       <c r="C499" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D499" t="str">
         <v>2567</v>
@@ -8890,7 +8890,7 @@
         <v>นายมูฮำหมัด สะอาด</v>
       </c>
       <c r="C500" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D500" t="str">
         <v>2567</v>
@@ -8907,7 +8907,7 @@
         <v>นายรีฟฮาน สือรี</v>
       </c>
       <c r="C501" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D501" t="str">
         <v>2567</v>
@@ -8924,7 +8924,7 @@
         <v>นายวรกฤษณ์ โกษาแสง</v>
       </c>
       <c r="C502" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D502" t="str">
         <v>2567</v>
@@ -8941,7 +8941,7 @@
         <v>นายสะอั๊ด แสนพรม</v>
       </c>
       <c r="C503" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D503" t="str">
         <v>2567</v>
@@ -8958,7 +8958,7 @@
         <v>นายหาดี กาเต๊ะ</v>
       </c>
       <c r="C504" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D504" t="str">
         <v>2567</v>
@@ -8975,7 +8975,7 @@
         <v>นายอับดุลวาริส มามะ</v>
       </c>
       <c r="C505" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D505" t="str">
         <v>2567</v>
@@ -8992,7 +8992,7 @@
         <v>นายอับบาส หลังเถาะ</v>
       </c>
       <c r="C506" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D506" t="str">
         <v>2567</v>
@@ -9009,7 +9009,7 @@
         <v>นายอัสมี่ หมัดนะฮู</v>
       </c>
       <c r="C507" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D507" t="str">
         <v>2567</v>
@@ -9026,7 +9026,7 @@
         <v>นายอาลาวีย์ หลีอาหมัด</v>
       </c>
       <c r="C508" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D508" t="str">
         <v>2567</v>
@@ -9043,7 +9043,7 @@
         <v>นายอิลฮัม วาเฮงฮารง</v>
       </c>
       <c r="C509" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D509" t="str">
         <v>2567</v>
@@ -9060,7 +9060,7 @@
         <v>นายอิลฮัม วาเฮงฮารง</v>
       </c>
       <c r="C510" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D510" t="str">
         <v>2567</v>
@@ -9077,7 +9077,7 @@
         <v>นายเอกนรินทร์ ภักดี</v>
       </c>
       <c r="C511" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D511" t="str">
         <v>2567</v>
@@ -9094,7 +9094,7 @@
         <v>นายฮัมดี กาเต๊ะ</v>
       </c>
       <c r="C512" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D512" t="str">
         <v>2567</v>
@@ -9111,7 +9111,7 @@
         <v>นายฮัสบี เจ๊ะโน๊ะ</v>
       </c>
       <c r="C513" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D513" t="str">
         <v>2567</v>
@@ -9128,7 +9128,7 @@
         <v>นายอับดุลมุมีน หะดาตู</v>
       </c>
       <c r="C514" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D514" t="str">
         <v>2567</v>
@@ -9145,7 +9145,7 @@
         <v>นางสาวซาวานี ดามาเร๊าะ</v>
       </c>
       <c r="C515" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D515" t="str">
         <v>2567</v>
@@ -9162,7 +9162,7 @@
         <v>นางสาวณริณี มะโซ๊ะ</v>
       </c>
       <c r="C516" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D516" t="str">
         <v>2567</v>
@@ -9179,7 +9179,7 @@
         <v>นางสาวณีดะอ์ บินเจ๊ะเลาะ</v>
       </c>
       <c r="C517" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D517" t="str">
         <v>2567</v>
@@ -9196,7 +9196,7 @@
         <v>นางสาวนาวาล จึเลาะ</v>
       </c>
       <c r="C518" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D518" t="str">
         <v>2567</v>
@@ -9213,7 +9213,7 @@
         <v>นางสาวนุชญาฮาญ หมัดอะดัม</v>
       </c>
       <c r="C519" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D519" t="str">
         <v>2567</v>
@@ -9230,7 +9230,7 @@
         <v>นางสาวนูรซูไฮลา ยามานอ</v>
       </c>
       <c r="C520" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D520" t="str">
         <v>2567</v>
@@ -9247,7 +9247,7 @@
         <v>นางสาวพาตีฮะ แวอุเซ็ง</v>
       </c>
       <c r="C521" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D521" t="str">
         <v>2567</v>
@@ -9264,7 +9264,7 @@
         <v>นางสาวฟาเดีย หะ</v>
       </c>
       <c r="C522" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D522" t="str">
         <v>2567</v>
@@ -9281,7 +9281,7 @@
         <v>นางสาวฟาตีฮะห์ สะอิด</v>
       </c>
       <c r="C523" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D523" t="str">
         <v>2567</v>
@@ -9298,7 +9298,7 @@
         <v>นางสาวมุมตัส เป็นแหละแหนะ</v>
       </c>
       <c r="C524" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D524" t="str">
         <v>2567</v>
@@ -9315,7 +9315,7 @@
         <v>นางสาวรอยฮาน บือโต</v>
       </c>
       <c r="C525" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D525" t="str">
         <v>2567</v>
@@ -9332,7 +9332,7 @@
         <v>นางสาวรูซีลา บาโงย</v>
       </c>
       <c r="C526" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D526" t="str">
         <v>2567</v>
@@ -9349,7 +9349,7 @@
         <v>นางสาวรูวัยดา วาเละ</v>
       </c>
       <c r="C527" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D527" t="str">
         <v>2567</v>
@@ -9366,7 +9366,7 @@
         <v>นางสาวโรศิลา เตาวะโต</v>
       </c>
       <c r="C528" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D528" t="str">
         <v>2567</v>
@@ -9383,7 +9383,7 @@
         <v>นางสาววาฟาอ์ เจ๊ะเห็ง</v>
       </c>
       <c r="C529" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D529" t="str">
         <v>2567</v>
@@ -9400,7 +9400,7 @@
         <v>นางสาววาฟาอฺ บินมามะ</v>
       </c>
       <c r="C530" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D530" t="str">
         <v>2567</v>
@@ -9417,7 +9417,7 @@
         <v>นางสาวอนาตาสา ยูโซะ</v>
       </c>
       <c r="C531" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D531" t="str">
         <v>2567</v>
@@ -9434,7 +9434,7 @@
         <v>นางสาวอภิชญา ธิยัน</v>
       </c>
       <c r="C532" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D532" t="str">
         <v>2567</v>
@@ -9451,7 +9451,7 @@
         <v>นางสาวอัจฉรา ช้างเพชร</v>
       </c>
       <c r="C533" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D533" t="str">
         <v>2567</v>
@@ -9468,7 +9468,7 @@
         <v>นางสาวอัสมะ เจ๊ะเล็ง</v>
       </c>
       <c r="C534" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D534" t="str">
         <v>2567</v>
@@ -9485,7 +9485,7 @@
         <v>นางสาวอัสมา ปรีชาชนะกุล</v>
       </c>
       <c r="C535" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D535" t="str">
         <v>2567</v>
@@ -9502,7 +9502,7 @@
         <v>นางสาวอามีนะห์ ดอเล๊าะ</v>
       </c>
       <c r="C536" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D536" t="str">
         <v>2567</v>
@@ -9519,7 +9519,7 @@
         <v>นางสาวฮัสมา หลำเบ็ญสะ</v>
       </c>
       <c r="C537" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D537" t="str">
         <v>2567</v>
@@ -9536,7 +9536,7 @@
         <v>นางสาวลาฏีฟา เศษระนำ</v>
       </c>
       <c r="C538" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D538" t="str">
         <v>2567</v>
@@ -9553,7 +9553,7 @@
         <v>นายอโนชา ลือแบซา</v>
       </c>
       <c r="C539" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D539" t="str">
         <v>2567</v>
@@ -9570,7 +9570,7 @@
         <v>นายอาบูลูคมาน บาราเฮง</v>
       </c>
       <c r="C540" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D540" t="str">
         <v>2567</v>
@@ -9587,7 +9587,7 @@
         <v>นายวีรากร อาหมัด</v>
       </c>
       <c r="C541" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D541" t="str">
         <v>2567</v>
@@ -9604,7 +9604,7 @@
         <v>นางสาวจีรนันท์ จันทิปะ</v>
       </c>
       <c r="C542" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D542" t="str">
         <v>2567</v>
@@ -9621,7 +9621,7 @@
         <v>นางสาวซอบารียะห์ บูละ</v>
       </c>
       <c r="C543" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D543" t="str">
         <v>2567</v>
@@ -9638,7 +9638,7 @@
         <v>นางสาวซานาอ์ เจะมะแซ</v>
       </c>
       <c r="C544" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D544" t="str">
         <v>2567</v>
@@ -9655,7 +9655,7 @@
         <v>นางสาวซาฟีน๊ะ ฮะยีบิลัง</v>
       </c>
       <c r="C545" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D545" t="str">
         <v>2567</v>
@@ -9672,7 +9672,7 @@
         <v>นางสาวตักวา เจ๊ะมี</v>
       </c>
       <c r="C546" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D546" t="str">
         <v>2567</v>
@@ -9689,7 +9689,7 @@
         <v>นางสาวนิชธาวัลย์ ดารากัย</v>
       </c>
       <c r="C547" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D547" t="str">
         <v>2567</v>
@@ -9706,7 +9706,7 @@
         <v>นางสาวนุรฮายาตี สาแล๊ะ</v>
       </c>
       <c r="C548" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D548" t="str">
         <v>2567</v>
@@ -9723,7 +9723,7 @@
         <v>นางสาวนุสรา จินตรา</v>
       </c>
       <c r="C549" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D549" t="str">
         <v>2567</v>
@@ -9740,7 +9740,7 @@
         <v>นางสาวนูรีซัน อาบูบาซา</v>
       </c>
       <c r="C550" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D550" t="str">
         <v>2567</v>
@@ -9757,7 +9757,7 @@
         <v>นางสาวนูรุลฟิรดาวส์ แหม๊ะ</v>
       </c>
       <c r="C551" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D551" t="str">
         <v>2567</v>
@@ -9774,7 +9774,7 @@
         <v>นางสาวโนร์เดีย เจะมูซอ</v>
       </c>
       <c r="C552" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D552" t="str">
         <v>2567</v>
@@ -9791,7 +9791,7 @@
         <v>นางสาวฟาติน ดอเลาะ</v>
       </c>
       <c r="C553" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D553" t="str">
         <v>2567</v>
@@ -9808,7 +9808,7 @@
         <v>นางสาวฟิรดาวส์ ยะผา</v>
       </c>
       <c r="C554" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D554" t="str">
         <v>2567</v>
@@ -9825,7 +9825,7 @@
         <v>นางสาวมุมีนะห์ สาแมง</v>
       </c>
       <c r="C555" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D555" t="str">
         <v>2567</v>
@@ -9842,7 +9842,7 @@
         <v>นางสาวแวซูไฮลา เปาะเฮาะ</v>
       </c>
       <c r="C556" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D556" t="str">
         <v>2567</v>
@@ -9859,7 +9859,7 @@
         <v>นางสาวหทัยภัทร โต๊ะเส็น</v>
       </c>
       <c r="C557" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D557" t="str">
         <v>2567</v>
@@ -9876,7 +9876,7 @@
         <v>นางสาวอนุตตรีย์ ปะหนะ</v>
       </c>
       <c r="C558" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D558" t="str">
         <v>2567</v>
@@ -9893,7 +9893,7 @@
         <v>นางสาวอัฟนาน เจะแม</v>
       </c>
       <c r="C559" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D559" t="str">
         <v>2567</v>
@@ -9910,7 +9910,7 @@
         <v>นางสาวอัฟนาน สูงใหญ่</v>
       </c>
       <c r="C560" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D560" t="str">
         <v>2567</v>
@@ -9927,7 +9927,7 @@
         <v>นางสาวอัฟฟานี สะแลแม</v>
       </c>
       <c r="C561" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D561" t="str">
         <v>2567</v>
@@ -9944,7 +9944,7 @@
         <v>นางสาวอามีลา ดอเต๊ะ</v>
       </c>
       <c r="C562" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D562" t="str">
         <v>2567</v>
@@ -9961,7 +9961,7 @@
         <v>นางสาวอารีน่า เล๊าะยีตา</v>
       </c>
       <c r="C563" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D563" t="str">
         <v>2567</v>
@@ -9978,7 +9978,7 @@
         <v>นางสาวฮะนีฟะฮ์ มะมิน</v>
       </c>
       <c r="C564" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D564" t="str">
         <v>2567</v>
@@ -9995,7 +9995,7 @@
         <v>นางสาวฮาซานะห์ ซารี</v>
       </c>
       <c r="C565" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D565" t="str">
         <v>2567</v>
@@ -10012,7 +10012,7 @@
         <v>นางสาวฮาน่า กาซัน</v>
       </c>
       <c r="C566" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D566" t="str">
         <v>2567</v>
@@ -10029,7 +10029,7 @@
         <v>นางสาวฮาลีเม๊าะ หะยีเจ๊ะมิง</v>
       </c>
       <c r="C567" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D567" t="str">
         <v>2567</v>
@@ -10046,7 +10046,7 @@
         <v>นางสาวซูเฟีย มะแซ</v>
       </c>
       <c r="C568" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D568" t="str">
         <v>2567</v>
@@ -10063,7 +10063,7 @@
         <v>นางสาวกุลนิดา มะกะหลี</v>
       </c>
       <c r="C569" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D569" t="str">
         <v>2567</v>
@@ -10080,7 +10080,7 @@
         <v>นายซอมัด ลิวัลย์</v>
       </c>
       <c r="C570" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D570" t="str">
         <v>2567</v>
@@ -10097,7 +10097,7 @@
         <v>นายนครินทร์ หวันด้าเหร่</v>
       </c>
       <c r="C571" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D571" t="str">
         <v>2567</v>
@@ -10114,7 +10114,7 @@
         <v>นายบัดรี่ สีแก้วอ่อน</v>
       </c>
       <c r="C572" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D572" t="str">
         <v>2567</v>
@@ -10131,7 +10131,7 @@
         <v>นายพงพัฒน์ จันทร์ย่อง</v>
       </c>
       <c r="C573" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D573" t="str">
         <v>2567</v>
@@ -10148,7 +10148,7 @@
         <v>นายภาสกร หมานเส้ง</v>
       </c>
       <c r="C574" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D574" t="str">
         <v>2567</v>
@@ -10165,7 +10165,7 @@
         <v>นายมูฮัมหมัดซุกรี วานิ</v>
       </c>
       <c r="C575" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D575" t="str">
         <v>2567</v>
@@ -10182,7 +10182,7 @@
         <v>นายมูฮัมหมัดอิกบาล บาโง</v>
       </c>
       <c r="C576" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D576" t="str">
         <v>2567</v>
@@ -10199,7 +10199,7 @@
         <v>นายหัซมีร์ มะเซ่ง</v>
       </c>
       <c r="C577" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D577" t="str">
         <v>2567</v>
@@ -10216,7 +10216,7 @@
         <v>นายอนัน พงษ์มุลี</v>
       </c>
       <c r="C578" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D578" t="str">
         <v>2567</v>
@@ -10233,7 +10233,7 @@
         <v>นายอารอฟัร ยีสะเอะ</v>
       </c>
       <c r="C579" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D579" t="str">
         <v>2567</v>
@@ -10250,7 +10250,7 @@
         <v>นายอารีฟีน กะโด</v>
       </c>
       <c r="C580" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D580" t="str">
         <v>2567</v>
@@ -10267,7 +10267,7 @@
         <v>นายอาสือมิง นิซาแย</v>
       </c>
       <c r="C581" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D581" t="str">
         <v>2567</v>
@@ -10284,7 +10284,7 @@
         <v>นายฮากีม ลือแบซา</v>
       </c>
       <c r="C582" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D582" t="str">
         <v>2567</v>
@@ -10301,7 +10301,7 @@
         <v>นางสาวกอนีตะฮ์ บัสตี</v>
       </c>
       <c r="C583" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D583" t="str">
         <v>2567</v>
@@ -10318,7 +10318,7 @@
         <v>นางสาวกัสมา เจะอูมา</v>
       </c>
       <c r="C584" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D584" t="str">
         <v>2567</v>
@@ -10335,7 +10335,7 @@
         <v>นางสาวกิตติยา บ้านควน</v>
       </c>
       <c r="C585" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D585" t="str">
         <v>2567</v>
@@ -10352,7 +10352,7 @@
         <v>นางสาวกุลนิดา มะกะหลี</v>
       </c>
       <c r="C586" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D586" t="str">
         <v>2567</v>
@@ -10369,7 +10369,7 @@
         <v>นางสาวเกษรา หมีนเหล็บ</v>
       </c>
       <c r="C587" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D587" t="str">
         <v>2567</v>
@@ -10386,7 +10386,7 @@
         <v>นางสาวซอลีฮะห์ สมาแห</v>
       </c>
       <c r="C588" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D588" t="str">
         <v>2567</v>
@@ -10403,7 +10403,7 @@
         <v>นางสาวซัลซาบีลา เจ๊ะเฮง</v>
       </c>
       <c r="C589" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D589" t="str">
         <v>2567</v>
@@ -10420,7 +10420,7 @@
         <v>นางสาวซัลวา ดอเลาะ</v>
       </c>
       <c r="C590" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D590" t="str">
         <v>2567</v>
@@ -10437,7 +10437,7 @@
         <v>นางสาวซารีนา แวอีซอ</v>
       </c>
       <c r="C591" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D591" t="str">
         <v>2567</v>
@@ -10454,7 +10454,7 @@
         <v>นางสาวซาฮีดะห์ ลือแบลูวง</v>
       </c>
       <c r="C592" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D592" t="str">
         <v>2567</v>
@@ -10471,7 +10471,7 @@
         <v>นางสาวซุลฟา ไสสากา</v>
       </c>
       <c r="C593" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D593" t="str">
         <v>2567</v>
@@ -10488,7 +10488,7 @@
         <v>นางสาวซูลฟา สาและ</v>
       </c>
       <c r="C594" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D594" t="str">
         <v>2567</v>
@@ -10505,7 +10505,7 @@
         <v>นางสาวโซเฟีย สาแม</v>
       </c>
       <c r="C595" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D595" t="str">
         <v>2567</v>
@@ -10522,7 +10522,7 @@
         <v>นางสาวไซฟิตา โดสนิ</v>
       </c>
       <c r="C596" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D596" t="str">
         <v>2567</v>
@@ -10539,7 +10539,7 @@
         <v>นางสาวต่วนฮานีฟา นิจิ</v>
       </c>
       <c r="C597" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D597" t="str">
         <v>2567</v>
@@ -10556,7 +10556,7 @@
         <v>นางสาวตัสนีม สาหะ</v>
       </c>
       <c r="C598" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D598" t="str">
         <v>2567</v>
@@ -10573,7 +10573,7 @@
         <v>นางสาวนดา เเมเร๊าะ</v>
       </c>
       <c r="C599" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D599" t="str">
         <v>2567</v>
@@ -10590,7 +10590,7 @@
         <v>นางสาวนัจญวา สนิ</v>
       </c>
       <c r="C600" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D600" t="str">
         <v>2567</v>
@@ -10607,7 +10607,7 @@
         <v>นางสาวนัจวา แสแตแล</v>
       </c>
       <c r="C601" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D601" t="str">
         <v>2567</v>
@@ -10624,7 +10624,7 @@
         <v>นางสาวนัญวา อารีหมาน</v>
       </c>
       <c r="C602" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D602" t="str">
         <v>2567</v>
@@ -10641,7 +10641,7 @@
         <v>นางสาวนาซอฟะห์ เจะและ</v>
       </c>
       <c r="C603" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D603" t="str">
         <v>2567</v>
@@ -10658,7 +10658,7 @@
         <v>นางสาวนาญีหะฮ์ บินเย็ง</v>
       </c>
       <c r="C604" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D604" t="str">
         <v>2567</v>
@@ -10675,7 +10675,7 @@
         <v>นางสาวนาเดีย อับดุลเล๊าะ</v>
       </c>
       <c r="C605" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D605" t="str">
         <v>2567</v>
@@ -10692,7 +10692,7 @@
         <v>นางสาวนาตาซาร์ มนทา</v>
       </c>
       <c r="C606" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D606" t="str">
         <v>2567</v>
@@ -10709,7 +10709,7 @@
         <v>นางสาวนาวาล มะรอเซะ</v>
       </c>
       <c r="C607" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D607" t="str">
         <v>2567</v>
@@ -10726,7 +10726,7 @@
         <v>นางสาวนิสรีน สีเย๊าะ</v>
       </c>
       <c r="C608" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D608" t="str">
         <v>2567</v>
@@ -10743,7 +10743,7 @@
         <v>นางสาวนุรมา วาหลง</v>
       </c>
       <c r="C609" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D609" t="str">
         <v>2567</v>
@@ -10760,7 +10760,7 @@
         <v>นางสาวนุรไลลาย์ สาเมาะ</v>
       </c>
       <c r="C610" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D610" t="str">
         <v>2567</v>
@@ -10777,7 +10777,7 @@
         <v>นางสาวนูซัยบะห์ เจะโซะ</v>
       </c>
       <c r="C611" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D611" t="str">
         <v>2567</v>
@@ -10794,7 +10794,7 @@
         <v>นางสาวนูซูลา จารง</v>
       </c>
       <c r="C612" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D612" t="str">
         <v>2567</v>
@@ -10811,7 +10811,7 @@
         <v>นางสาวนูญูม สุไลมาน</v>
       </c>
       <c r="C613" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D613" t="str">
         <v>2567</v>
@@ -10828,7 +10828,7 @@
         <v>นางสาวนูรฟิตรีดาว์ เจะหะ</v>
       </c>
       <c r="C614" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D614" t="str">
         <v>2567</v>
@@ -10845,7 +10845,7 @@
         <v>นางสาวนูรอัยซะห์ อาเเวกะจิ</v>
       </c>
       <c r="C615" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D615" t="str">
         <v>2567</v>
@@ -10862,7 +10862,7 @@
         <v>นางสาวนูรอีมาน วาบา</v>
       </c>
       <c r="C616" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D616" t="str">
         <v>2567</v>
@@ -10879,7 +10879,7 @@
         <v>นางสาวนูรฮีดายะห์ จักร์ปา</v>
       </c>
       <c r="C617" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D617" t="str">
         <v>2567</v>
@@ -10896,7 +10896,7 @@
         <v>นางสาวนูรุลอิฮ์ซาน บินหะยีคอเนาะ</v>
       </c>
       <c r="C618" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D618" t="str">
         <v>2567</v>
@@ -10913,7 +10913,7 @@
         <v>นางสาวนูรูณดา เจ๊ะดาโอ๊ะ</v>
       </c>
       <c r="C619" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D619" t="str">
         <v>2567</v>
@@ -10930,7 +10930,7 @@
         <v>นางสาวเนาวาร ดอเลาะ</v>
       </c>
       <c r="C620" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D620" t="str">
         <v>2567</v>
@@ -10947,7 +10947,7 @@
         <v>นางสาวบีบีฮัยฟาร์ อับดุลเลาะ</v>
       </c>
       <c r="C621" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D621" t="str">
         <v>2567</v>
@@ -10964,7 +10964,7 @@
         <v>นางสาวปุตรีบัลกีส ปาแนมาแล</v>
       </c>
       <c r="C622" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D622" t="str">
         <v>2567</v>
@@ -10981,7 +10981,7 @@
         <v>นางสาวฟรัยรุสฟาริน จารง</v>
       </c>
       <c r="C623" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D623" t="str">
         <v>2567</v>
@@ -10998,7 +10998,7 @@
         <v>นางสาวฟาติน ลาเตะ</v>
       </c>
       <c r="C624" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D624" t="str">
         <v>2567</v>
@@ -11015,7 +11015,7 @@
         <v>นางสาวฟีร์ญาณ ลาเต๊ะ</v>
       </c>
       <c r="C625" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D625" t="str">
         <v>2567</v>
@@ -11032,7 +11032,7 @@
         <v>นางสาวมัรญาน อูมา</v>
       </c>
       <c r="C626" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D626" t="str">
         <v>2567</v>
@@ -11049,7 +11049,7 @@
         <v>นางสาวมุมีนะฮ์ เจะโซะ</v>
       </c>
       <c r="C627" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D627" t="str">
         <v>2567</v>
@@ -11066,7 +11066,7 @@
         <v>นางสาวมูเนาวาเราะห์ กูโน</v>
       </c>
       <c r="C628" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D628" t="str">
         <v>2567</v>
@@ -11083,7 +11083,7 @@
         <v>นางสาวยัสมีน ยาแลกา</v>
       </c>
       <c r="C629" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D629" t="str">
         <v>2567</v>
@@ -11100,7 +11100,7 @@
         <v>นางสาวยาวานี ยีสาอิ</v>
       </c>
       <c r="C630" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D630" t="str">
         <v>2567</v>
@@ -11117,7 +11117,7 @@
         <v>นางสาวริฟฮาน กาหะมะ</v>
       </c>
       <c r="C631" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D631" t="str">
         <v>2567</v>
@@ -11134,7 +11134,7 @@
         <v>นางสาวลาฏีฟะฮ์ วิชา</v>
       </c>
       <c r="C632" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D632" t="str">
         <v>2567</v>
@@ -11151,7 +11151,7 @@
         <v>นางสาววาริศรา หง้าฝา</v>
       </c>
       <c r="C633" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D633" t="str">
         <v>2567</v>
@@ -11168,7 +11168,7 @@
         <v>นางสาววิดาด์ บัตรหมะ</v>
       </c>
       <c r="C634" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D634" t="str">
         <v>2567</v>
@@ -11185,7 +11185,7 @@
         <v>นางสาววีฟาก มะดอหะ</v>
       </c>
       <c r="C635" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D635" t="str">
         <v>2567</v>
@@ -11202,7 +11202,7 @@
         <v>นางสาวสาอีดะฮ์ วอเดร์</v>
       </c>
       <c r="C636" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D636" t="str">
         <v>2567</v>
@@ -11219,7 +11219,7 @@
         <v>นางสาวอรนลิน สามารถ</v>
       </c>
       <c r="C637" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D637" t="str">
         <v>2567</v>
@@ -11236,7 +11236,7 @@
         <v>นางสาวอัฟนาน มะดีเย๊าะ</v>
       </c>
       <c r="C638" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D638" t="str">
         <v>2567</v>
@@ -11253,7 +11253,7 @@
         <v>นางสาวอัสมะ วาเละ</v>
       </c>
       <c r="C639" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D639" t="str">
         <v>2567</v>
@@ -11270,7 +11270,7 @@
         <v>นางสาวอามาณี ยะหริ่ง</v>
       </c>
       <c r="C640" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D640" t="str">
         <v>2567</v>
@@ -11287,7 +11287,7 @@
         <v>นางสาวอามาลีน่า อับดุลมูตาเละ</v>
       </c>
       <c r="C641" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D641" t="str">
         <v>2567</v>
@@ -11304,7 +11304,7 @@
         <v>นางสาวอารีนี มะเซ็ง</v>
       </c>
       <c r="C642" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D642" t="str">
         <v>2567</v>
@@ -11321,7 +11321,7 @@
         <v>นางสาวอาลียา อับดุลวาฮับ</v>
       </c>
       <c r="C643" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D643" t="str">
         <v>2567</v>
@@ -11338,7 +11338,7 @@
         <v>นางสาวอาวาฎิฟ สือฆี</v>
       </c>
       <c r="C644" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D644" t="str">
         <v>2567</v>
@@ -11355,7 +11355,7 @@
         <v>นางสาวอินอาม นุ่งอาหลี</v>
       </c>
       <c r="C645" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D645" t="str">
         <v>2567</v>
@@ -11372,7 +11372,7 @@
         <v>นางสาวอินาส สาเมาะแม</v>
       </c>
       <c r="C646" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D646" t="str">
         <v>2567</v>
@@ -11389,7 +11389,7 @@
         <v>นางสาวอิฟฟัต ดารากัย</v>
       </c>
       <c r="C647" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D647" t="str">
         <v>2567</v>
@@ -11406,7 +11406,7 @@
         <v>นางสาวฮาซูนา หะระตี</v>
       </c>
       <c r="C648" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D648" t="str">
         <v>2567</v>
@@ -11423,7 +11423,7 @@
         <v>นางสาวฮิกมะฮฺ สะมะแอ</v>
       </c>
       <c r="C649" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D649" t="str">
         <v>2567</v>
@@ -11440,7 +11440,7 @@
         <v>นางสาวฮุสณีย์ มามะ</v>
       </c>
       <c r="C650" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D650" t="str">
         <v>2567</v>
@@ -11457,7 +11457,7 @@
         <v>นางสาวฮุสนียะฮ์ เจะเเว</v>
       </c>
       <c r="C651" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D651" t="str">
         <v>2567</v>
@@ -11474,7 +11474,7 @@
         <v>นางสาวนูรซัลวาร์ แลฮา</v>
       </c>
       <c r="C652" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D652" t="str">
         <v>2567</v>
@@ -11491,7 +11491,7 @@
         <v>นางสาวสีตีนูรฮารีซา สะเตง</v>
       </c>
       <c r="C653" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D653" t="str">
         <v>2567</v>
@@ -11508,7 +11508,7 @@
         <v>นางสาวโรศิลา เตาวะโต</v>
       </c>
       <c r="C654" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D654" t="str">
         <v>2567</v>
@@ -11525,7 +11525,7 @@
         <v>นายกรวัฒน์ ดวงตา</v>
       </c>
       <c r="C655" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D655" t="str">
         <v>2567</v>
@@ -11542,7 +11542,7 @@
         <v>นายนุรฮานูดีน ดอขา</v>
       </c>
       <c r="C656" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D656" t="str">
         <v>2567</v>
@@ -11559,7 +11559,7 @@
         <v>นายอับดุลมูบีน สะมะดะแมง</v>
       </c>
       <c r="C657" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D657" t="str">
         <v>2567</v>
@@ -11576,7 +11576,7 @@
         <v>นายอิรฮัม ยูโซ๊ะ</v>
       </c>
       <c r="C658" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D658" t="str">
         <v>2567</v>
@@ -11593,7 +11593,7 @@
         <v>นายวรวัฒน์ ภูมี</v>
       </c>
       <c r="C659" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D659" t="str">
         <v>2567</v>
@@ -11610,7 +11610,7 @@
         <v>นางสาวนาซูฮา สะมาแอ</v>
       </c>
       <c r="C660" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D660" t="str">
         <v>2567</v>
@@ -11627,7 +11627,7 @@
         <v>นางสาวฮาบีบะห์ สือรี</v>
       </c>
       <c r="C661" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D661" t="str">
         <v>2567</v>
@@ -11644,7 +11644,7 @@
         <v>นางสาวฮานาน หวันหมาน</v>
       </c>
       <c r="C662" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D662" t="str">
         <v>2567</v>
@@ -11661,7 +11661,7 @@
         <v>นางสาวยัสมี ลาเตะ</v>
       </c>
       <c r="C663" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D663" t="str">
         <v>2567</v>
@@ -11678,7 +11678,7 @@
         <v>นางสาวกนกนิภา หมื่นระย้า</v>
       </c>
       <c r="C664" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D664" t="str">
         <v>2567</v>
@@ -11695,7 +11695,7 @@
         <v>นางสาวกรกธ กวดจิตร</v>
       </c>
       <c r="C665" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D665" t="str">
         <v>2567</v>
@@ -11712,7 +11712,7 @@
         <v>นางสาวกูนาซีลา ต่วนตือเงาะ</v>
       </c>
       <c r="C666" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D666" t="str">
         <v>2567</v>
@@ -11729,7 +11729,7 @@
         <v>นางสาวเกาซัร มะลี</v>
       </c>
       <c r="C667" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D667" t="str">
         <v>2567</v>
@@ -11746,7 +11746,7 @@
         <v>นางสาวคูซัยมะฮ แวดือราแม</v>
       </c>
       <c r="C668" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D668" t="str">
         <v>2567</v>
@@ -11763,7 +11763,7 @@
         <v>นางสาวคูไซณี ยูโซ๊ะ</v>
       </c>
       <c r="C669" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D669" t="str">
         <v>2567</v>
@@ -11780,7 +11780,7 @@
         <v>นางสาวเจ๊ะนัสเราะห์ เซ็ง</v>
       </c>
       <c r="C670" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D670" t="str">
         <v>2567</v>
@@ -11797,7 +11797,7 @@
         <v>นางสาวซัมซียะห์ ซง</v>
       </c>
       <c r="C671" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D671" t="str">
         <v>2567</v>
@@ -11814,7 +11814,7 @@
         <v>นางสาวซัยมะห์ แซซู</v>
       </c>
       <c r="C672" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D672" t="str">
         <v>2567</v>
@@ -11831,7 +11831,7 @@
         <v>นางสาวซัลวา ลีแงตายี</v>
       </c>
       <c r="C673" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D673" t="str">
         <v>2567</v>
@@ -11848,7 +11848,7 @@
         <v>นางสาวซัสมี มะลี</v>
       </c>
       <c r="C674" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D674" t="str">
         <v>2567</v>
@@ -11865,7 +11865,7 @@
         <v>นางสาวซาฟีการ์ แวยูโซ๊ะ</v>
       </c>
       <c r="C675" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D675" t="str">
         <v>2567</v>
@@ -11882,7 +11882,7 @@
         <v>นางสาวซาฮาเร๊าะร์ เจ๊ะโซ๊ะ</v>
       </c>
       <c r="C676" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D676" t="str">
         <v>2567</v>
@@ -11899,7 +11899,7 @@
         <v>นางสาวซิลมี วุฒิสมัย</v>
       </c>
       <c r="C677" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D677" t="str">
         <v>2567</v>
@@ -11916,7 +11916,7 @@
         <v>นางสาวซีฟาร์ก มามะเร</v>
       </c>
       <c r="C678" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D678" t="str">
         <v>2567</v>
@@ -11933,7 +11933,7 @@
         <v>นางสาวซูรีนา สามะอาลี</v>
       </c>
       <c r="C679" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D679" t="str">
         <v>2567</v>
@@ -11950,7 +11950,7 @@
         <v>นางสาวณัฐวิภา หวันละโส๊ะ</v>
       </c>
       <c r="C680" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D680" t="str">
         <v>2567</v>
@@ -11967,7 +11967,7 @@
         <v>นางสาวดารุณี ดะแซ</v>
       </c>
       <c r="C681" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D681" t="str">
         <v>2567</v>
@@ -11984,7 +11984,7 @@
         <v>นางสาวเดียร์อาน่า วารีศรี</v>
       </c>
       <c r="C682" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D682" t="str">
         <v>2567</v>
@@ -12001,7 +12001,7 @@
         <v>นางสาวต่วนจูไวรียะฮ์ โตะกูบาฮา</v>
       </c>
       <c r="C683" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D683" t="str">
         <v>2567</v>
@@ -12018,7 +12018,7 @@
         <v>นางสาวต่วนนาดีลา นิและ</v>
       </c>
       <c r="C684" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D684" t="str">
         <v>2567</v>
@@ -12035,7 +12035,7 @@
         <v>นางสาวต่วนอัลวานี ปาเเซ</v>
       </c>
       <c r="C685" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D685" t="str">
         <v>2567</v>
@@ -12052,7 +12052,7 @@
         <v>นางสาวตัสนีม ดอฆอ</v>
       </c>
       <c r="C686" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D686" t="str">
         <v>2567</v>
@@ -12069,7 +12069,7 @@
         <v>นางสาวตัสนีม ตือปิงหม๊ะ</v>
       </c>
       <c r="C687" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D687" t="str">
         <v>2567</v>
@@ -12086,7 +12086,7 @@
         <v>นางสาวตัสนีม บาโด</v>
       </c>
       <c r="C688" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D688" t="str">
         <v>2567</v>
@@ -12103,7 +12103,7 @@
         <v>นางสาวตัสมีน ทุมมาลี</v>
       </c>
       <c r="C689" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D689" t="str">
         <v>2567</v>
@@ -12120,7 +12120,7 @@
         <v>นางสาวตาสูบีเราะห์ แล๊ะ</v>
       </c>
       <c r="C690" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D690" t="str">
         <v>2567</v>
@@ -12137,7 +12137,7 @@
         <v>นางสาวนราดา โต๊ะหมัด</v>
       </c>
       <c r="C691" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D691" t="str">
         <v>2567</v>
@@ -12154,7 +12154,7 @@
         <v>นางสาวนัจวา สาเมาะ</v>
       </c>
       <c r="C692" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D692" t="str">
         <v>2567</v>
@@ -12171,7 +12171,7 @@
         <v>นางสาวนัจวา วันอุสมาน</v>
       </c>
       <c r="C693" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D693" t="str">
         <v>2567</v>
@@ -12188,7 +12188,7 @@
         <v>นางสาวนัซเราะฮ์ มะแซ</v>
       </c>
       <c r="C694" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D694" t="str">
         <v>2567</v>
@@ -12205,7 +12205,7 @@
         <v>นางสาวนัดดา หะสาเมาะ</v>
       </c>
       <c r="C695" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D695" t="str">
         <v>2567</v>
@@ -12222,7 +12222,7 @@
         <v>นางสาวนัสรินดา โม๊ะ</v>
       </c>
       <c r="C696" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D696" t="str">
         <v>2567</v>
@@ -12239,7 +12239,7 @@
         <v>นางสาวนัสรีน ดือราแม</v>
       </c>
       <c r="C697" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D697" t="str">
         <v>2567</v>
@@ -12256,7 +12256,7 @@
         <v>นางสาวฟิรดาวซ์ เจ๊ะแล</v>
       </c>
       <c r="C698" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D698" t="str">
         <v>2567</v>
@@ -12273,7 +12273,7 @@
         <v>นางสาวนาจูวา บาโด</v>
       </c>
       <c r="C699" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D699" t="str">
         <v>2567</v>
@@ -12290,7 +12290,7 @@
         <v>นางสาวนาซีละห์ ยูนุ๊</v>
       </c>
       <c r="C700" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D700" t="str">
         <v>2567</v>
@@ -12307,7 +12307,7 @@
         <v>นางสาวนาเดีย บู๊กุ</v>
       </c>
       <c r="C701" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D701" t="str">
         <v>2567</v>
@@ -12324,7 +12324,7 @@
         <v>นางสาวนาอีมี ตาบา</v>
       </c>
       <c r="C702" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D702" t="str">
         <v>2567</v>
@@ -12341,7 +12341,7 @@
         <v>นางสาวนุรฟาตีนี มะลี</v>
       </c>
       <c r="C703" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D703" t="str">
         <v>2567</v>
@@ -12358,7 +12358,7 @@
         <v>นางสาวนุรฮายาตี จารง</v>
       </c>
       <c r="C704" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D704" t="str">
         <v>2567</v>
@@ -12375,7 +12375,7 @@
         <v>นางสาวนูรเดียนาฮ์ สาเม๊าะ</v>
       </c>
       <c r="C705" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D705" t="str">
         <v>2567</v>
@@ -12392,7 +12392,7 @@
         <v>นางสาวนูรฟาติน ดอฆอ</v>
       </c>
       <c r="C706" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D706" t="str">
         <v>2567</v>
@@ -12409,7 +12409,7 @@
         <v>นางสาวนูรฟาตีฮะ สาและ</v>
       </c>
       <c r="C707" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D707" t="str">
         <v>2567</v>
@@ -12426,7 +12426,7 @@
         <v>นางสาวนูรยะห์ สาแม็ง</v>
       </c>
       <c r="C708" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D708" t="str">
         <v>2567</v>
@@ -12443,7 +12443,7 @@
         <v>นางสาวนูร์อีมาล ยูโซะ</v>
       </c>
       <c r="C709" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D709" t="str">
         <v>2567</v>
@@ -12460,7 +12460,7 @@
         <v>นางสาวนูรีฮูไซนาห์ อาแว</v>
       </c>
       <c r="C710" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D710" t="str">
         <v>2567</v>
@@ -12477,7 +12477,7 @@
         <v>นางสาวโนร์ซาฮีระห์ อูเซ็ง</v>
       </c>
       <c r="C711" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D711" t="str">
         <v>2567</v>
@@ -12494,7 +12494,7 @@
         <v>นางสาวปาลิดา ธานมาศ</v>
       </c>
       <c r="C712" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D712" t="str">
         <v>2567</v>
@@ -12511,7 +12511,7 @@
         <v>นางสาวมารีอา มาเยอะ</v>
       </c>
       <c r="C713" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D713" t="str">
         <v>2567</v>
@@ -12528,7 +12528,7 @@
         <v>นางสาวมุสลีมะห์ บือแน</v>
       </c>
       <c r="C714" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D714" t="str">
         <v>2567</v>
@@ -12545,7 +12545,7 @@
         <v>นางสาวมุสลีฮา มูซอ</v>
       </c>
       <c r="C715" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D715" t="str">
         <v>2567</v>
@@ -12562,7 +12562,7 @@
         <v>นางสาวยามีละห์ ยาสามิง</v>
       </c>
       <c r="C716" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D716" t="str">
         <v>2567</v>
@@ -12579,7 +12579,7 @@
         <v>นางสาวรอฎียา มหาศานติ</v>
       </c>
       <c r="C717" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D717" t="str">
         <v>2567</v>
@@ -12596,7 +12596,7 @@
         <v>นางสาวรอยมี่ ปูสาอะ</v>
       </c>
       <c r="C718" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D718" t="str">
         <v>2567</v>
@@ -12613,7 +12613,7 @@
         <v>นางสาวรุลณะดาร์ ซือรี</v>
       </c>
       <c r="C719" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D719" t="str">
         <v>2567</v>
@@ -12630,7 +12630,7 @@
         <v>นางสาวรุสณีย์ เตะเมาะ</v>
       </c>
       <c r="C720" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D720" t="str">
         <v>2567</v>
@@ -12647,7 +12647,7 @@
         <v>นางสาวลนิตา บูนำ</v>
       </c>
       <c r="C721" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D721" t="str">
         <v>2567</v>
@@ -12664,7 +12664,7 @@
         <v>นางสาวลาตีฟะธ์ อาแวจิ</v>
       </c>
       <c r="C722" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D722" t="str">
         <v>2567</v>
@@ -12681,7 +12681,7 @@
         <v>นางสาวลินลนา บูเกะเจ๊ะลี</v>
       </c>
       <c r="C723" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D723" t="str">
         <v>2567</v>
@@ -12698,7 +12698,7 @@
         <v>นางสาววรรณิสา เหมรา</v>
       </c>
       <c r="C724" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D724" t="str">
         <v>2567</v>
@@ -12715,7 +12715,7 @@
         <v>นางสาววันอานีส แวลาเต๊ะ</v>
       </c>
       <c r="C725" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D725" t="str">
         <v>2567</v>
@@ -12732,7 +12732,7 @@
         <v>นางสาววานีดา สือแม็ง</v>
       </c>
       <c r="C726" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D726" t="str">
         <v>2567</v>
@@ -12749,7 +12749,7 @@
         <v>นางสาววีร์อาม ลาเตะ</v>
       </c>
       <c r="C727" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D727" t="str">
         <v>2567</v>
@@ -12766,7 +12766,7 @@
         <v>นางสาววีอาร์ม เจะบู</v>
       </c>
       <c r="C728" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D728" t="str">
         <v>2567</v>
@@ -12783,7 +12783,7 @@
         <v>นางสาวแวโนรอาย์ แวดอเลาะ</v>
       </c>
       <c r="C729" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D729" t="str">
         <v>2567</v>
@@ -12800,7 +12800,7 @@
         <v>นางสาวศรีดา รักโอ</v>
       </c>
       <c r="C730" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D730" t="str">
         <v>2567</v>
@@ -12817,7 +12817,7 @@
         <v>นางสาวศูมัยยะห์ มะมิง</v>
       </c>
       <c r="C731" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D731" t="str">
         <v>2567</v>
@@ -12834,7 +12834,7 @@
         <v>นางสาวสานียา วาจิ</v>
       </c>
       <c r="C732" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D732" t="str">
         <v>2567</v>
@@ -12851,7 +12851,7 @@
         <v>นางสาวอะฟาฟ บูงอ</v>
       </c>
       <c r="C733" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D733" t="str">
         <v>2567</v>
@@ -12868,7 +12868,7 @@
         <v>นางสาวอัฟนาน โตะโยะ</v>
       </c>
       <c r="C734" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D734" t="str">
         <v>2567</v>
@@ -12885,7 +12885,7 @@
         <v>นางสาวอัลวานี สาแม</v>
       </c>
       <c r="C735" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D735" t="str">
         <v>2567</v>
@@ -12902,7 +12902,7 @@
         <v>นางสาวอาซียะห์ โต๊ะลีกง</v>
       </c>
       <c r="C736" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D736" t="str">
         <v>2567</v>
@@ -12919,7 +12919,7 @@
         <v>นางสาวอาซูรา แยนา</v>
       </c>
       <c r="C737" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D737" t="str">
         <v>2567</v>
@@ -12936,7 +12936,7 @@
         <v>นางสาวอาตีระห์ มอลอ</v>
       </c>
       <c r="C738" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D738" t="str">
         <v>2567</v>
@@ -12953,7 +12953,7 @@
         <v>นางสาวอามานี หมาดเต๊ะ</v>
       </c>
       <c r="C739" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D739" t="str">
         <v>2567</v>
@@ -12970,7 +12970,7 @@
         <v>นางสาวอามีนี สาแม</v>
       </c>
       <c r="C740" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D740" t="str">
         <v>2567</v>
@@ -12987,7 +12987,7 @@
         <v>นางสาวอารีนี แวกือจิ</v>
       </c>
       <c r="C741" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D741" t="str">
         <v>2567</v>
@@ -13004,7 +13004,7 @@
         <v>นางสาวอาอีฉะ จิเระ</v>
       </c>
       <c r="C742" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D742" t="str">
         <v>2567</v>
@@ -13021,7 +13021,7 @@
         <v>นางสาวอุลยา มะสาพา</v>
       </c>
       <c r="C743" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D743" t="str">
         <v>2567</v>
@@ -13038,7 +13038,7 @@
         <v>นางสาวฮาลีเม๊าะ ตือปิงหม๊ะ</v>
       </c>
       <c r="C744" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D744" t="str">
         <v>2567</v>
@@ -13055,7 +13055,7 @@
         <v>นางสาวฮูซนา มะรือสะ</v>
       </c>
       <c r="C745" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D745" t="str">
         <v>2567</v>
@@ -13072,7 +13072,7 @@
         <v>นางสาวฮูสนา ยามา</v>
       </c>
       <c r="C746" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D746" t="str">
         <v>2567</v>
@@ -13089,7 +13089,7 @@
         <v>นางสาวไฮฟา โตะมะ</v>
       </c>
       <c r="C747" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D747" t="str">
         <v>2567</v>
@@ -13106,7 +13106,7 @@
         <v>นางสาวนาซูฮา สะมาแอ</v>
       </c>
       <c r="C748" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D748" t="str">
         <v>2567</v>
@@ -13123,7 +13123,7 @@
         <v>นางสาวกูฟิรดาวส์ สาอิ</v>
       </c>
       <c r="C749" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D749" t="str">
         <v>2567</v>
@@ -13140,7 +13140,7 @@
         <v>นางสาวฟาตีมะห์ สาแมง</v>
       </c>
       <c r="C750" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D750" t="str">
         <v>2567</v>
@@ -13157,7 +13157,7 @@
         <v>นางสาวลาฏีฟา เศษระนำ</v>
       </c>
       <c r="C751" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D751" t="str">
         <v>2567</v>
@@ -13174,7 +13174,7 @@
         <v>นางสาวธมลวรรณ แซ่ย่าง</v>
       </c>
       <c r="C752" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D752" t="str">
         <v>2567</v>
@@ -13191,7 +13191,7 @@
         <v>นางสาวฟาตีฮะห์ สะอิด</v>
       </c>
       <c r="C753" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D753" t="str">
         <v>2567</v>
@@ -13208,7 +13208,7 @@
         <v>นางสาวอัฟนาน มะดีเย๊าะ</v>
       </c>
       <c r="C754" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D754" t="str">
         <v>2567</v>
@@ -13225,7 +13225,7 @@
         <v>นายคอยรุลฮีซัม หะยีเจ๊ะเต๊ะ</v>
       </c>
       <c r="C755" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D755" t="str">
         <v>2568</v>
@@ -13242,7 +13242,7 @@
         <v>นายต่วนอัมรี ลอจิ</v>
       </c>
       <c r="C756" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D756" t="str">
         <v>2568</v>
@@ -13259,7 +13259,7 @@
         <v>นายต่วนฮาบีบุรรอฮ์มัน ตีงี</v>
       </c>
       <c r="C757" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D757" t="str">
         <v>2568</v>
@@ -13276,7 +13276,7 @@
         <v>นายนัจญมี สนิ</v>
       </c>
       <c r="C758" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D758" t="str">
         <v>2568</v>
@@ -13293,7 +13293,7 @@
         <v>นายนาอีม สะกะแย</v>
       </c>
       <c r="C759" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D759" t="str">
         <v>2568</v>
@@ -13310,7 +13310,7 @@
         <v>นายฟะฮ์มีย์ วาราวอ</v>
       </c>
       <c r="C760" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D760" t="str">
         <v>2568</v>
@@ -13327,7 +13327,7 @@
         <v>นายมุคลิศ สาเระ</v>
       </c>
       <c r="C761" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D761" t="str">
         <v>2568</v>
@@ -13344,7 +13344,7 @@
         <v>นายมูฮันหนัด ซีดิ</v>
       </c>
       <c r="C762" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D762" t="str">
         <v>2568</v>
@@ -13361,7 +13361,7 @@
         <v>นายมูฮัมมัดเฟาซาน เจะสนิ</v>
       </c>
       <c r="C763" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D763" t="str">
         <v>2568</v>
@@ -13378,7 +13378,7 @@
         <v>นายสุไลมาน จอหวัง</v>
       </c>
       <c r="C764" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D764" t="str">
         <v>2568</v>
@@ -13395,7 +13395,7 @@
         <v>นายอนัส หะมะ</v>
       </c>
       <c r="C765" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D765" t="str">
         <v>2568</v>
@@ -13412,7 +13412,7 @@
         <v>นายอะฮ์ลาม เจะมะ</v>
       </c>
       <c r="C766" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D766" t="str">
         <v>2568</v>
@@ -13429,7 +13429,7 @@
         <v>นายอัฟนาน พงค์หลง</v>
       </c>
       <c r="C767" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D767" t="str">
         <v>2568</v>
@@ -13446,7 +13446,7 @@
         <v>นายอามีน หะยีหะซา</v>
       </c>
       <c r="C768" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D768" t="str">
         <v>2568</v>
@@ -13463,7 +13463,7 @@
         <v>นายอิลฮัม โฮมียอ</v>
       </c>
       <c r="C769" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D769" t="str">
         <v>2568</v>
@@ -13480,7 +13480,7 @@
         <v>นายฮานาฟี เจ๊ะดอเลาะ</v>
       </c>
       <c r="C770" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D770" t="str">
         <v>2568</v>
@@ -13497,7 +13497,7 @@
         <v>นายฮานีฟ บินมิง</v>
       </c>
       <c r="C771" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D771" t="str">
         <v>2568</v>
@@ -13514,7 +13514,7 @@
         <v>นายดานิช ณ ปัตตานี</v>
       </c>
       <c r="C772" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D772" t="str">
         <v>2568</v>
@@ -13531,7 +13531,7 @@
         <v>นายอามีร หะยีปิยวงศ์</v>
       </c>
       <c r="C773" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D773" t="str">
         <v>2568</v>
@@ -13548,7 +13548,7 @@
         <v>นายอิมรอน แวนะไล</v>
       </c>
       <c r="C774" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D774" t="str">
         <v>2568</v>
@@ -13565,7 +13565,7 @@
         <v>นายซอและฮ์ สาแม็ง</v>
       </c>
       <c r="C775" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D775" t="str">
         <v>2568</v>
@@ -13582,7 +13582,7 @@
         <v>นางสาวชาฮีดะห์ สกุลา</v>
       </c>
       <c r="C776" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D776" t="str">
         <v>2568</v>
@@ -13599,7 +13599,7 @@
         <v>นางสาวชีรีน อาเเวเงาะ</v>
       </c>
       <c r="C777" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D777" t="str">
         <v>2568</v>
@@ -13616,7 +13616,7 @@
         <v>นางสาวซาฮาด๊ะ อูมา</v>
       </c>
       <c r="C778" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D778" t="str">
         <v>2568</v>
@@ -13633,7 +13633,7 @@
         <v>นางสาวนัจญมี สันเพชร</v>
       </c>
       <c r="C779" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D779" t="str">
         <v>2568</v>
@@ -13650,7 +13650,7 @@
         <v>นางสาวนาซีนีน มูเก็ม</v>
       </c>
       <c r="C780" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D780" t="str">
         <v>2568</v>
@@ -13667,7 +13667,7 @@
         <v>นางสาวนูรฟาตี อาแซ</v>
       </c>
       <c r="C781" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D781" t="str">
         <v>2568</v>
@@ -13684,7 +13684,7 @@
         <v>นางสาวนูรูลอาดียา มามะ</v>
       </c>
       <c r="C782" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D782" t="str">
         <v>2568</v>
@@ -13701,7 +13701,7 @@
         <v>นางสาวนูรูลอิซซะห์ ตะโละดิง</v>
       </c>
       <c r="C783" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D783" t="str">
         <v>2568</v>
@@ -13718,7 +13718,7 @@
         <v>นางสาวผ้าทอ ปรีดาพิริยะ</v>
       </c>
       <c r="C784" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D784" t="str">
         <v>2568</v>
@@ -13735,7 +13735,7 @@
         <v>นางสาวฟิฏรียะห์ ยูโซ๊ะ</v>
       </c>
       <c r="C785" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D785" t="str">
         <v>2568</v>
@@ -13752,7 +13752,7 @@
         <v>นางสาวมุสลีมะห์ เปาะซา</v>
       </c>
       <c r="C786" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D786" t="str">
         <v>2568</v>
@@ -13769,7 +13769,7 @@
         <v>นางสาวยัสมีน ยาโงะ</v>
       </c>
       <c r="C787" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D787" t="str">
         <v>2568</v>
@@ -13786,7 +13786,7 @@
         <v>นางสาวลาวิลน่า นิยมเดชา</v>
       </c>
       <c r="C788" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D788" t="str">
         <v>2568</v>
@@ -13803,7 +13803,7 @@
         <v>นางสาววาฟ๊ะ นาราวัน</v>
       </c>
       <c r="C789" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D789" t="str">
         <v>2568</v>
@@ -13820,7 +13820,7 @@
         <v>นางสาวแวรอซีดา ลงเน๊าะ</v>
       </c>
       <c r="C790" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D790" t="str">
         <v>2568</v>
@@ -13837,7 +13837,7 @@
         <v>นางสาวอานีตา สาหลำ</v>
       </c>
       <c r="C791" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D791" t="str">
         <v>2568</v>
@@ -13854,7 +13854,7 @@
         <v>นางสาวฮุสณา ยานยา</v>
       </c>
       <c r="C792" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>อิสลามศึกษา</v>
       </c>
       <c r="D792" t="str">
         <v>2568</v>
@@ -13871,7 +13871,7 @@
         <v>นายกูอุสมาน ลอนิ</v>
       </c>
       <c r="C793" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D793" t="str">
         <v>2568</v>
@@ -13888,7 +13888,7 @@
         <v>นายดานิซ ณ ปัตตานี</v>
       </c>
       <c r="C794" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D794" t="str">
         <v>2568</v>
@@ -13905,7 +13905,7 @@
         <v>นายนัจญมุดดีน เด็น</v>
       </c>
       <c r="C795" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D795" t="str">
         <v>2568</v>
@@ -13922,7 +13922,7 @@
         <v>นายพิทวัส หมะ</v>
       </c>
       <c r="C796" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D796" t="str">
         <v>2568</v>
@@ -13939,7 +13939,7 @@
         <v>นายเฟาซาน อาแซ</v>
       </c>
       <c r="C797" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D797" t="str">
         <v>2568</v>
@@ -13956,7 +13956,7 @@
         <v>นายเฟาซี รองปาน</v>
       </c>
       <c r="C798" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D798" t="str">
         <v>2568</v>
@@ -13973,7 +13973,7 @@
         <v>นายมูฮัมหมัดชารีฟ หลังปุเต๊ะ</v>
       </c>
       <c r="C799" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D799" t="str">
         <v>2568</v>
@@ -13990,7 +13990,7 @@
         <v>นายมูฮัมหมัดฮากิม โกะจับ</v>
       </c>
       <c r="C800" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D800" t="str">
         <v>2568</v>
@@ -14007,7 +14007,7 @@
         <v>นายวิลฎาน โดยหมะ</v>
       </c>
       <c r="C801" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D801" t="str">
         <v>2568</v>
@@ -14024,7 +14024,7 @@
         <v>นายอาซา คาล่า</v>
       </c>
       <c r="C802" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D802" t="str">
         <v>2568</v>
@@ -14041,7 +14041,7 @@
         <v>นายอารอฟัต เบ็นแหละแหนะ</v>
       </c>
       <c r="C803" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D803" t="str">
         <v>2568</v>
@@ -14058,7 +14058,7 @@
         <v>นายดารุสดีน อุ่นเรือน</v>
       </c>
       <c r="C804" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D804" t="str">
         <v>2568</v>
@@ -14075,7 +14075,7 @@
         <v>นายวินทกร อุมารี</v>
       </c>
       <c r="C805" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D805" t="str">
         <v>2568</v>
@@ -14092,7 +14092,7 @@
         <v>นางสาวกอยยีมะห์ ลือเย๊าะ</v>
       </c>
       <c r="C806" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D806" t="str">
         <v>2568</v>
@@ -14109,7 +14109,7 @@
         <v>นางสาวตักวา บาโด</v>
       </c>
       <c r="C807" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D807" t="str">
         <v>2568</v>
@@ -14126,7 +14126,7 @@
         <v>นางสาวตัสนีม หมาดโส๊ะ</v>
       </c>
       <c r="C808" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D808" t="str">
         <v>2568</v>
@@ -14143,7 +14143,7 @@
         <v>นางสาวเนตรนภา โล๊ะซอ</v>
       </c>
       <c r="C809" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D809" t="str">
         <v>2568</v>
@@ -14160,7 +14160,7 @@
         <v>นางสาวรอไฮฟา บือราเฮง</v>
       </c>
       <c r="C810" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D810" t="str">
         <v>2568</v>
@@ -14177,7 +14177,7 @@
         <v>นางสาวลลิตา คงเดิม</v>
       </c>
       <c r="C811" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D811" t="str">
         <v>2568</v>
@@ -14194,7 +14194,7 @@
         <v>นางสาวศศิตา ธูปหอม</v>
       </c>
       <c r="C812" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D812" t="str">
         <v>2568</v>
@@ -14211,7 +14211,7 @@
         <v>นางสาวณัทวรรณ เมืองเล่ง</v>
       </c>
       <c r="C813" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอาหรับ</v>
       </c>
       <c r="D813" t="str">
         <v>2568</v>
@@ -14228,7 +14228,7 @@
         <v>นายซอดีกีน หลังจิ</v>
       </c>
       <c r="C814" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D814" t="str">
         <v>2568</v>
@@ -14245,7 +14245,7 @@
         <v>นายฟัรฮาน ตียะห์</v>
       </c>
       <c r="C815" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D815" t="str">
         <v>2568</v>
@@ -14262,7 +14262,7 @@
         <v>นายอามีรูลฮาซัน โทโม</v>
       </c>
       <c r="C816" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D816" t="str">
         <v>2568</v>
@@ -14279,7 +14279,7 @@
         <v>นายอิลฮัม ยามา</v>
       </c>
       <c r="C817" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D817" t="str">
         <v>2568</v>
@@ -14296,7 +14296,7 @@
         <v>นางสาวกุลนันทน์ ลีมะ</v>
       </c>
       <c r="C818" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D818" t="str">
         <v>2568</v>
@@ -14313,7 +14313,7 @@
         <v>นางสาวซามีมี อาลี</v>
       </c>
       <c r="C819" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D819" t="str">
         <v>2568</v>
@@ -14330,7 +14330,7 @@
         <v>นางสาวยุซรอ มูซอ</v>
       </c>
       <c r="C820" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D820" t="str">
         <v>2568</v>
@@ -14347,7 +14347,7 @@
         <v>นางสาวอากีดะฮ ยามา</v>
       </c>
       <c r="C821" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D821" t="str">
         <v>2568</v>
@@ -14364,7 +14364,7 @@
         <v>นางสาวอามานี ดอเลาะ</v>
       </c>
       <c r="C822" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D822" t="str">
         <v>2568</v>
@@ -14381,7 +14381,7 @@
         <v>นางสาวฮันนาน โตะลู</v>
       </c>
       <c r="C823" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D823" t="str">
         <v>2568</v>
@@ -14398,7 +14398,7 @@
         <v>นางสาวซากีนะห์ มาหะมะ</v>
       </c>
       <c r="C824" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D824" t="str">
         <v>2568</v>
@@ -14415,7 +14415,7 @@
         <v>นางสาวอิลฮามี่ ลาเตะ</v>
       </c>
       <c r="C825" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>วิทยาศาสตร์ทั่วไป</v>
       </c>
       <c r="D825" t="str">
         <v>2568</v>
@@ -14432,7 +14432,7 @@
         <v>นายซอบีร สูหลง</v>
       </c>
       <c r="C826" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D826" t="str">
         <v>2568</v>
@@ -14449,7 +14449,7 @@
         <v>นายนิอับดุลฟารีส นิแว</v>
       </c>
       <c r="C827" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D827" t="str">
         <v>2568</v>
@@ -14466,7 +14466,7 @@
         <v>นายนิอับดุลฮากิม หะยีนิมะ</v>
       </c>
       <c r="C828" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D828" t="str">
         <v>2568</v>
@@ -14483,7 +14483,7 @@
         <v>นายนิฮัยซาม อาลี</v>
       </c>
       <c r="C829" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D829" t="str">
         <v>2568</v>
@@ -14500,7 +14500,7 @@
         <v>นายบุนยามีน ยีกา</v>
       </c>
       <c r="C830" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D830" t="str">
         <v>2568</v>
@@ -14517,7 +14517,7 @@
         <v>นายฟัครี สาเร๊ะ</v>
       </c>
       <c r="C831" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D831" t="str">
         <v>2568</v>
@@ -14534,7 +14534,7 @@
         <v>นายมูฮัมหมัด มะเซ็ง</v>
       </c>
       <c r="C832" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D832" t="str">
         <v>2568</v>
@@ -14551,7 +14551,7 @@
         <v>นายยูซุฟ ฮะยีบิลัง</v>
       </c>
       <c r="C833" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D833" t="str">
         <v>2568</v>
@@ -14568,7 +14568,7 @@
         <v>นายรุสลัน ยีสะอิ</v>
       </c>
       <c r="C834" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D834" t="str">
         <v>2568</v>
@@ -14585,7 +14585,7 @@
         <v>นายวซีม ฮาซาณัณท์</v>
       </c>
       <c r="C835" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D835" t="str">
         <v>2568</v>
@@ -14602,7 +14602,7 @@
         <v>นายอนัส อาแซ</v>
       </c>
       <c r="C836" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D836" t="str">
         <v>2568</v>
@@ -14619,7 +14619,7 @@
         <v>นายอะฏียะ ฮานาฟี</v>
       </c>
       <c r="C837" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D837" t="str">
         <v>2568</v>
@@ -14636,7 +14636,7 @@
         <v>นายอะฮ์หมัด มะดอมะ</v>
       </c>
       <c r="C838" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D838" t="str">
         <v>2568</v>
@@ -14653,7 +14653,7 @@
         <v>นายอักบาล หะยีวาลี</v>
       </c>
       <c r="C839" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D839" t="str">
         <v>2568</v>
@@ -14670,7 +14670,7 @@
         <v>นายอัฟนัน นาแว</v>
       </c>
       <c r="C840" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D840" t="str">
         <v>2568</v>
@@ -14687,7 +14687,7 @@
         <v>นายอิลฮัม มูเซะ</v>
       </c>
       <c r="C841" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D841" t="str">
         <v>2568</v>
@@ -14704,7 +14704,7 @@
         <v>นายอีบาดุลเลาะห์ มูซอ</v>
       </c>
       <c r="C842" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D842" t="str">
         <v>2568</v>
@@ -14721,7 +14721,7 @@
         <v>นายฮาวารี มะแซ</v>
       </c>
       <c r="C843" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D843" t="str">
         <v>2568</v>
@@ -14738,7 +14738,7 @@
         <v>นายมูฮัยมิน คาเร็ง</v>
       </c>
       <c r="C844" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D844" t="str">
         <v>2568</v>
@@ -14755,7 +14755,7 @@
         <v>นายอับดุสสลาม บูงา</v>
       </c>
       <c r="C845" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D845" t="str">
         <v>2568</v>
@@ -14772,7 +14772,7 @@
         <v>นางสาวกอนีตะห์ สะละสอ</v>
       </c>
       <c r="C846" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D846" t="str">
         <v>2568</v>
@@ -14789,7 +14789,7 @@
         <v>นางสาวเกาซัร ดอเลาะ</v>
       </c>
       <c r="C847" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D847" t="str">
         <v>2568</v>
@@ -14806,7 +14806,7 @@
         <v>นางสาวซัลมา นุ้ยสมัน</v>
       </c>
       <c r="C848" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D848" t="str">
         <v>2568</v>
@@ -14823,7 +14823,7 @@
         <v>นางสาวซัลวา สาและ</v>
       </c>
       <c r="C849" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D849" t="str">
         <v>2568</v>
@@ -14840,7 +14840,7 @@
         <v>นางสาวซัลวา หลำหม๊ะ</v>
       </c>
       <c r="C850" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D850" t="str">
         <v>2568</v>
@@ -14857,7 +14857,7 @@
         <v>นางสาวซีตีนูรฮารีซา ดอเลาะ</v>
       </c>
       <c r="C851" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D851" t="str">
         <v>2568</v>
@@ -14874,7 +14874,7 @@
         <v>นางสาวซุฟฟียา บีดิง</v>
       </c>
       <c r="C852" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D852" t="str">
         <v>2568</v>
@@ -14891,7 +14891,7 @@
         <v>นางสาวกูอัฟนาน โตะกูตือเงาะ</v>
       </c>
       <c r="C853" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D853" t="str">
         <v>2568</v>
@@ -14908,7 +14908,7 @@
         <v>นางสาวตักวา ตะโล๊ะเลาะ</v>
       </c>
       <c r="C854" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D854" t="str">
         <v>2568</v>
@@ -14925,7 +14925,7 @@
         <v>นางสาวตัสนีม ยาโงะ</v>
       </c>
       <c r="C855" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D855" t="str">
         <v>2568</v>
@@ -14942,7 +14942,7 @@
         <v>นางสาวตัสนีม สาและ</v>
       </c>
       <c r="C856" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D856" t="str">
         <v>2568</v>
@@ -14959,7 +14959,7 @@
         <v>นางสาวนัจญมี สารณะ</v>
       </c>
       <c r="C857" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D857" t="str">
         <v>2568</v>
@@ -14976,7 +14976,7 @@
         <v>นางสาวนัจมิน เปาะเลาะ</v>
       </c>
       <c r="C858" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D858" t="str">
         <v>2568</v>
@@ -14993,7 +14993,7 @@
         <v>นางสาวนิวาฮีดา ดอเล๊าะ</v>
       </c>
       <c r="C859" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D859" t="str">
         <v>2568</v>
@@ -15010,7 +15010,7 @@
         <v>นางสาวนูรซีรีน เจะหะ</v>
       </c>
       <c r="C860" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D860" t="str">
         <v>2568</v>
@@ -15027,7 +15027,7 @@
         <v>นางสาวนูรฟาตีนา เจ๊ะดาโอ๊ะ</v>
       </c>
       <c r="C861" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D861" t="str">
         <v>2568</v>
@@ -15044,7 +15044,7 @@
         <v>นางสาวนูรฟาตีมี ซะซา</v>
       </c>
       <c r="C862" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D862" t="str">
         <v>2568</v>
@@ -15061,7 +15061,7 @@
         <v>นางสาวนูรอีมาน สะแต</v>
       </c>
       <c r="C863" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D863" t="str">
         <v>2568</v>
@@ -15078,7 +15078,7 @@
         <v>นางสาวนูรฮาลีซา หะยีกิจิ</v>
       </c>
       <c r="C864" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D864" t="str">
         <v>2568</v>
@@ -15095,7 +15095,7 @@
         <v>นางสาวนูรฮุดา สุขเอียด</v>
       </c>
       <c r="C865" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D865" t="str">
         <v>2568</v>
@@ -15112,7 +15112,7 @@
         <v>นางสาวนูรีฮัน ลาเตะ</v>
       </c>
       <c r="C866" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D866" t="str">
         <v>2568</v>
@@ -15129,7 +15129,7 @@
         <v>นางสาวฟัฏตู ราแดง</v>
       </c>
       <c r="C867" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D867" t="str">
         <v>2568</v>
@@ -15146,7 +15146,7 @@
         <v>นางสาวฟาตีมะห์ เจะโซะ</v>
       </c>
       <c r="C868" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D868" t="str">
         <v>2568</v>
@@ -15163,7 +15163,7 @@
         <v>นางสาวฟาตีหะฮ์ เกาะแจ</v>
       </c>
       <c r="C869" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D869" t="str">
         <v>2568</v>
@@ -15180,7 +15180,7 @@
         <v>นางสาวฟาอีซะห์ อาบู</v>
       </c>
       <c r="C870" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D870" t="str">
         <v>2568</v>
@@ -15197,7 +15197,7 @@
         <v>นางสาวมัฆฟีเร๊าะห์ ยามา</v>
       </c>
       <c r="C871" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D871" t="str">
         <v>2568</v>
@@ -15214,7 +15214,7 @@
         <v>นางสาวมีรฝะห์ เจ๊ะแอสะนุง</v>
       </c>
       <c r="C872" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D872" t="str">
         <v>2568</v>
@@ -15231,7 +15231,7 @@
         <v>นางสาวมุกีย์ตา ลาได</v>
       </c>
       <c r="C873" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D873" t="str">
         <v>2568</v>
@@ -15248,7 +15248,7 @@
         <v>นางสาวมุมีนะห์ ยีดิง</v>
       </c>
       <c r="C874" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D874" t="str">
         <v>2568</v>
@@ -15265,7 +15265,7 @@
         <v>นางสาวมุสลีฮะห์ โซ๊ะนิยาดะ</v>
       </c>
       <c r="C875" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D875" t="str">
         <v>2568</v>
@@ -15282,7 +15282,7 @@
         <v>นางสาวยัสมีร์ บือนา</v>
       </c>
       <c r="C876" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D876" t="str">
         <v>2568</v>
@@ -15299,7 +15299,7 @@
         <v>นางสาวร็อยมี ยูโซะ</v>
       </c>
       <c r="C877" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D877" t="str">
         <v>2568</v>
@@ -15316,7 +15316,7 @@
         <v>นางสาวรอวิญา อาลดานียาล</v>
       </c>
       <c r="C878" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D878" t="str">
         <v>2568</v>
@@ -15333,7 +15333,7 @@
         <v>นางสาวรัยญาน สาเมาะ</v>
       </c>
       <c r="C879" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D879" t="str">
         <v>2568</v>
@@ -15350,7 +15350,7 @@
         <v>นางสาวซูไรยา หะยีลาเปะ</v>
       </c>
       <c r="C880" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D880" t="str">
         <v>2568</v>
@@ -15367,7 +15367,7 @@
         <v>นางสาวบิลคีส โสะขาว</v>
       </c>
       <c r="C881" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D881" t="str">
         <v>2568</v>
@@ -15384,7 +15384,7 @@
         <v>นางสาววัลญา เเหละหลี</v>
       </c>
       <c r="C882" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D882" t="str">
         <v>2568</v>
@@ -15401,7 +15401,7 @@
         <v>นางสาววิลดาณี มามะ</v>
       </c>
       <c r="C883" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D883" t="str">
         <v>2568</v>
@@ -15418,7 +15418,7 @@
         <v>นางสาวอนันดา มานะ</v>
       </c>
       <c r="C884" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D884" t="str">
         <v>2568</v>
@@ -15435,7 +15435,7 @@
         <v>นางสาวอัซวาณีย์ มหะมะ</v>
       </c>
       <c r="C885" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D885" t="str">
         <v>2568</v>
@@ -15452,7 +15452,7 @@
         <v>นางสาวอันดา เล๊าะหวัง</v>
       </c>
       <c r="C886" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D886" t="str">
         <v>2568</v>
@@ -15469,7 +15469,7 @@
         <v>นางสาวอัฟนาณ หะยีอับดุลเลาะ</v>
       </c>
       <c r="C887" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D887" t="str">
         <v>2568</v>
@@ -15486,7 +15486,7 @@
         <v>นางสาวอัรวา คงเหล่า</v>
       </c>
       <c r="C888" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D888" t="str">
         <v>2568</v>
@@ -15503,7 +15503,7 @@
         <v>นางสาวอัรวา มามะ</v>
       </c>
       <c r="C889" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D889" t="str">
         <v>2568</v>
@@ -15520,7 +15520,7 @@
         <v>นางสาวอานิส ยีมันใบ</v>
       </c>
       <c r="C890" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D890" t="str">
         <v>2568</v>
@@ -15537,7 +15537,7 @@
         <v>นางสาวอามีเนาะ ซิสาแม</v>
       </c>
       <c r="C891" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D891" t="str">
         <v>2568</v>
@@ -15554,7 +15554,7 @@
         <v>นางสาวอิมตินาน หะยีอาแซ</v>
       </c>
       <c r="C892" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D892" t="str">
         <v>2568</v>
@@ -15571,7 +15571,7 @@
         <v>นางสาวอีนัซ อับดุลเล๊าะ</v>
       </c>
       <c r="C893" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D893" t="str">
         <v>2568</v>
@@ -15588,7 +15588,7 @@
         <v>นางสาวฮนีฟา มามะ</v>
       </c>
       <c r="C894" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D894" t="str">
         <v>2568</v>
@@ -15605,7 +15605,7 @@
         <v>นางสาวนูไฝลี เมาตี</v>
       </c>
       <c r="C895" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D895" t="str">
         <v>2568</v>
@@ -15622,7 +15622,7 @@
         <v>นางสาวนูรอัสมะ มามะแตหะ</v>
       </c>
       <c r="C896" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D896" t="str">
         <v>2568</v>
@@ -15639,7 +15639,7 @@
         <v>นางสาวนูรฟัจรีย์ ดาแลเบาะ</v>
       </c>
       <c r="C897" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษาอังกฤษ</v>
       </c>
       <c r="D897" t="str">
         <v>2568</v>
@@ -15656,7 +15656,7 @@
         <v>นายอารีฟีน โตะโด</v>
       </c>
       <c r="C898" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D898" t="str">
         <v>2568</v>
@@ -15673,7 +15673,7 @@
         <v>นายซอลีฮิม ขามิ๊</v>
       </c>
       <c r="C899" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D899" t="str">
         <v>2568</v>
@@ -15690,7 +15690,7 @@
         <v>นางสาวมิสบะห์ สาแล๊ะ</v>
       </c>
       <c r="C900" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D900" t="str">
         <v>2568</v>
@@ -15707,7 +15707,7 @@
         <v>นางสาวอัสมาอฺ ดือราแม</v>
       </c>
       <c r="C901" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>ภาษามลายูและเทคโนโลยีการศึกษา</v>
       </c>
       <c r="D901" t="str">
         <v>2568</v>
@@ -15724,7 +15724,7 @@
         <v>นางสาวการีมะห์ มะลิหมัด</v>
       </c>
       <c r="C902" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D902" t="str">
         <v>2568</v>
@@ -15741,7 +15741,7 @@
         <v>นางสาวซราวาตุลอะห์ลัม เซ๊ะ</v>
       </c>
       <c r="C903" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D903" t="str">
         <v>2568</v>
@@ -15758,7 +15758,7 @@
         <v>นางสาวซอลีฮ๊ะ โตสแน</v>
       </c>
       <c r="C904" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D904" t="str">
         <v>2568</v>
@@ -15775,7 +15775,7 @@
         <v>นางสาวซัลวา อาลีมะสะ</v>
       </c>
       <c r="C905" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D905" t="str">
         <v>2568</v>
@@ -15792,7 +15792,7 @@
         <v>นางสาวซูฮัยละห์ เซ็ง</v>
       </c>
       <c r="C906" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D906" t="str">
         <v>2568</v>
@@ -15809,7 +15809,7 @@
         <v>นางสาวซูฮัยลา อาลี</v>
       </c>
       <c r="C907" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D907" t="str">
         <v>2568</v>
@@ -15826,7 +15826,7 @@
         <v>นางสาวดารินทร์ รักดี</v>
       </c>
       <c r="C908" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D908" t="str">
         <v>2568</v>
@@ -15843,7 +15843,7 @@
         <v>นางสาวดาลิยา บิลยะลา</v>
       </c>
       <c r="C909" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D909" t="str">
         <v>2568</v>
@@ -15860,7 +15860,7 @@
         <v>นางสาวต่วนฮานีซะห์ ตาหยง</v>
       </c>
       <c r="C910" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D910" t="str">
         <v>2568</v>
@@ -15877,7 +15877,7 @@
         <v>นางสาวตักวา เจะแว</v>
       </c>
       <c r="C911" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D911" t="str">
         <v>2568</v>
@@ -15894,7 +15894,7 @@
         <v>นางสาวตัสนีม ฮาแว</v>
       </c>
       <c r="C912" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D912" t="str">
         <v>2568</v>
@@ -15911,7 +15911,7 @@
         <v>นางสาวนอร์ไอนี จิตมั่น</v>
       </c>
       <c r="C913" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D913" t="str">
         <v>2568</v>
@@ -15928,7 +15928,7 @@
         <v>นางสาวนัจญานี พัชนี</v>
       </c>
       <c r="C914" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D914" t="str">
         <v>2568</v>
@@ -15945,7 +15945,7 @@
         <v>นางสาวนาดา สายวารี</v>
       </c>
       <c r="C915" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D915" t="str">
         <v>2568</v>
@@ -15962,7 +15962,7 @@
         <v>นางสาวนาดีลา หะยีกาเล็ง</v>
       </c>
       <c r="C916" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D916" t="str">
         <v>2568</v>
@@ -15979,7 +15979,7 @@
         <v>นางสาวนิซูใบกะห์ นิโซะ</v>
       </c>
       <c r="C917" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D917" t="str">
         <v>2568</v>
@@ -15996,7 +15996,7 @@
         <v>นางสาวนิสรีน ยาบี</v>
       </c>
       <c r="C918" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D918" t="str">
         <v>2568</v>
@@ -16013,7 +16013,7 @@
         <v>นางสาวนีดะอ์ ปาแด</v>
       </c>
       <c r="C919" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D919" t="str">
         <v>2568</v>
@@ -16030,7 +16030,7 @@
         <v>นางสาวนุรฮีดายะห์ อาบัส</v>
       </c>
       <c r="C920" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D920" t="str">
         <v>2568</v>
@@ -16047,7 +16047,7 @@
         <v>นางสาวนูรฟาตีนี บือโต</v>
       </c>
       <c r="C921" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D921" t="str">
         <v>2568</v>
@@ -16064,7 +16064,7 @@
         <v>นางสาวนูรฟาตีนี สาและ</v>
       </c>
       <c r="C922" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D922" t="str">
         <v>2568</v>
@@ -16081,7 +16081,7 @@
         <v>นางสาวนูรอามานี ยะโก๊ะ</v>
       </c>
       <c r="C923" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D923" t="str">
         <v>2568</v>
@@ -16098,7 +16098,7 @@
         <v>นางสาวนูรไอนี วาแม</v>
       </c>
       <c r="C924" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D924" t="str">
         <v>2568</v>
@@ -16115,7 +16115,7 @@
         <v>นางสาวนูรฮามีมี บูกุ</v>
       </c>
       <c r="C925" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D925" t="str">
         <v>2568</v>
@@ -16132,7 +16132,7 @@
         <v>นางสาวนูรฮายาตี กามะเด็ง</v>
       </c>
       <c r="C926" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D926" t="str">
         <v>2568</v>
@@ -16149,7 +16149,7 @@
         <v>นางสาวนูรฮูดา ติลามานิ</v>
       </c>
       <c r="C927" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D927" t="str">
         <v>2568</v>
@@ -16166,7 +16166,7 @@
         <v>นางสาวนูรฮูดา เตาวะโต</v>
       </c>
       <c r="C928" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D928" t="str">
         <v>2568</v>
@@ -16183,7 +16183,7 @@
         <v>นางสาวนูรฮูดา สิเดะ</v>
       </c>
       <c r="C929" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D929" t="str">
         <v>2568</v>
@@ -16200,7 +16200,7 @@
         <v>นางสาวนูรุลนัจญมีย์ มูฮัมหมัดกาเซ็ม</v>
       </c>
       <c r="C930" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D930" t="str">
         <v>2568</v>
@@ -16217,7 +16217,7 @@
         <v>นางสาวนูรูลนีสะ ยูโซ๊ะ</v>
       </c>
       <c r="C931" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D931" t="str">
         <v>2568</v>
@@ -16234,7 +16234,7 @@
         <v>นางสาวฟารินทร์ดา เจ๊ะอุบง</v>
       </c>
       <c r="C932" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D932" t="str">
         <v>2568</v>
@@ -16251,7 +16251,7 @@
         <v>นางสาวเนาวัร หามะ</v>
       </c>
       <c r="C933" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D933" t="str">
         <v>2568</v>
@@ -16268,7 +16268,7 @@
         <v>นางสาวโนรฟาติน ดาโอ๊ะ</v>
       </c>
       <c r="C934" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D934" t="str">
         <v>2568</v>
@@ -16285,7 +16285,7 @@
         <v>นางสาวพาอีซะ แวหะยี</v>
       </c>
       <c r="C935" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D935" t="str">
         <v>2568</v>
@@ -16302,7 +16302,7 @@
         <v>นางสาวฟาดีลาห์ แต</v>
       </c>
       <c r="C936" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D936" t="str">
         <v>2568</v>
@@ -16319,7 +16319,7 @@
         <v>นางสาวฟาตีนี ดากอฮา</v>
       </c>
       <c r="C937" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D937" t="str">
         <v>2568</v>
@@ -16336,7 +16336,7 @@
         <v>นางสาวฟาตีมะฮ์ อาแซ</v>
       </c>
       <c r="C938" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D938" t="str">
         <v>2568</v>
@@ -16353,7 +16353,7 @@
         <v>นางสาวฟารีซา เจะแต</v>
       </c>
       <c r="C939" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D939" t="str">
         <v>2568</v>
@@ -16370,7 +16370,7 @@
         <v>นางสาวฟาอีซะห์ อาบู</v>
       </c>
       <c r="C940" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D940" t="str">
         <v>2568</v>
@@ -16387,7 +16387,7 @@
         <v>นางสาวมารญาน สอมอนิอามะ</v>
       </c>
       <c r="C941" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D941" t="str">
         <v>2568</v>
@@ -16404,7 +16404,7 @@
         <v>นางสาวมุมีนะห์ เจ๊ะมะ</v>
       </c>
       <c r="C942" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D942" t="str">
         <v>2568</v>
@@ -16421,7 +16421,7 @@
         <v>นางสาวมุมีนะห์ มาโซ</v>
       </c>
       <c r="C943" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D943" t="str">
         <v>2568</v>
@@ -16438,7 +16438,7 @@
         <v>นางสาวมุมีนะฮ์ มาหนะ</v>
       </c>
       <c r="C944" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D944" t="str">
         <v>2568</v>
@@ -16455,7 +16455,7 @@
         <v>นางสาวยูสนีดาร์ บีรู</v>
       </c>
       <c r="C945" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D945" t="str">
         <v>2568</v>
@@ -16472,7 +16472,7 @@
         <v>นางสาวรอยยาน อารง</v>
       </c>
       <c r="C946" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D946" t="str">
         <v>2568</v>
@@ -16489,7 +16489,7 @@
         <v>นางสาวร็อยยาน สูแน</v>
       </c>
       <c r="C947" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D947" t="str">
         <v>2568</v>
@@ -16506,7 +16506,7 @@
         <v>นางสาวรอยฮาณ ซารูโว๊ะ</v>
       </c>
       <c r="C948" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D948" t="str">
         <v>2568</v>
@@ -16523,7 +16523,7 @@
         <v>นางสาววาฟ้า อิสมาเเอล</v>
       </c>
       <c r="C949" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D949" t="str">
         <v>2568</v>
@@ -16540,7 +16540,7 @@
         <v>นางสาววีอาม แมะ</v>
       </c>
       <c r="C950" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D950" t="str">
         <v>2568</v>
@@ -16557,7 +16557,7 @@
         <v>นางสาวแวซีตีฮายาร ดูมีแด</v>
       </c>
       <c r="C951" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D951" t="str">
         <v>2568</v>
@@ -16574,7 +16574,7 @@
         <v>นางสาวอามีเนาะฮ์ เองตาร์</v>
       </c>
       <c r="C952" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D952" t="str">
         <v>2568</v>
@@ -16591,7 +16591,7 @@
         <v>นางสาวสาฟูรา สิเดะ</v>
       </c>
       <c r="C953" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D953" t="str">
         <v>2568</v>
@@ -16608,7 +16608,7 @@
         <v>นางสาวอัยนาอ์ บิลและ</v>
       </c>
       <c r="C954" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D954" t="str">
         <v>2568</v>
@@ -16625,7 +16625,7 @@
         <v>นางสาวอัสมะ สะมะแอ</v>
       </c>
       <c r="C955" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D955" t="str">
         <v>2568</v>
@@ -16642,7 +16642,7 @@
         <v>นางสาวอาฟาฟ โดสนิ</v>
       </c>
       <c r="C956" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D956" t="str">
         <v>2568</v>
@@ -16659,7 +16659,7 @@
         <v>นางสาวอามีเราะ อิสดูเร๊ะ</v>
       </c>
       <c r="C957" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D957" t="str">
         <v>2568</v>
@@ -16676,7 +16676,7 @@
         <v>นางสาวอิฟฟะห์ เต๊ะมาลอ</v>
       </c>
       <c r="C958" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D958" t="str">
         <v>2568</v>
@@ -16693,7 +16693,7 @@
         <v>นางสาวอิลฮาม ยามา</v>
       </c>
       <c r="C959" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D959" t="str">
         <v>2568</v>
@@ -16710,7 +16710,7 @@
         <v>นางสาวอุมมุอัยมัญ บุญยาวีร์</v>
       </c>
       <c r="C960" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D960" t="str">
         <v>2568</v>
@@ -16727,7 +16727,7 @@
         <v>นางสาวฮัยฟาอ์ ดารามะ</v>
       </c>
       <c r="C961" t="str">
-        <v>ไม่ระบุสาขา</v>
+        <v>การศึกษาปฐมวัย</v>
       </c>
       <c r="D961" t="str">
         <v>2568</v>
